--- a/data/templates/templateData1D.xlsx
+++ b/data/templates/templateData1D.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27726"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/f215465b21b5e6e2/Studium/34_Github/TherMOS/data/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/f215465b21b5e6e2/Studium/34_Github/TherMOS/data/templates/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="174" documentId="8_{F43E7870-A1A1-4F05-86D5-E80884C51B87}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AD8F2A6F-2CEE-4625-AA33-AE073E0F48A1}"/>
+  <xr:revisionPtr revIDLastSave="202" documentId="8_{F43E7870-A1A1-4F05-86D5-E80884C51B87}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{554F36CC-A63B-4361-A52D-6D0B5169E226}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16896" activeTab="4" xr2:uid="{CD9970EB-652A-4818-A45C-836344967348}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16896" xr2:uid="{CD9970EB-652A-4818-A45C-836344967348}"/>
   </bookViews>
   <sheets>
     <sheet name="readme" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="148" uniqueCount="58">
   <si>
     <t>Date</t>
   </si>
@@ -165,9 +165,6 @@
     <t>Custom input feature 2</t>
   </si>
   <si>
-    <t>Custom input feature 3</t>
-  </si>
-  <si>
     <t>R1</t>
   </si>
   <si>
@@ -183,13 +180,40 @@
     <t>Custom response 2</t>
   </si>
   <si>
-    <t>Custom response 3</t>
-  </si>
-  <si>
     <t>W</t>
   </si>
   <si>
     <t>degC</t>
+  </si>
+  <si>
+    <t>O1</t>
+  </si>
+  <si>
+    <t>O2</t>
+  </si>
+  <si>
+    <t>On</t>
+  </si>
+  <si>
+    <t>Custom reference 1</t>
+  </si>
+  <si>
+    <t>Custom reference 2</t>
+  </si>
+  <si>
+    <t>Custom reference n</t>
+  </si>
+  <si>
+    <t>Custom response n</t>
+  </si>
+  <si>
+    <t>Custom input feature n</t>
+  </si>
+  <si>
+    <t>08.09.2024</t>
+  </si>
+  <si>
+    <t>Adding reference/offset value</t>
   </si>
 </sst>
 </file>
@@ -403,21 +427,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="34">
+  <cellXfs count="36">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
@@ -428,14 +443,13 @@
     <xf numFmtId="0" fontId="0" fillId="5" borderId="7" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="12" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -447,7 +461,7 @@
     <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -459,7 +473,25 @@
     <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -790,7 +822,7 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>16</v>
+        <v>56</v>
       </c>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.3">
@@ -837,11 +869,11 @@
       <c r="F13" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="J13" s="5" t="s">
+      <c r="J13" s="29" t="s">
         <v>17</v>
       </c>
-      <c r="K13" s="6"/>
-      <c r="L13" s="7"/>
+      <c r="K13" s="30"/>
+      <c r="L13" s="31"/>
     </row>
     <row r="14" spans="1:12" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A14" s="4">
@@ -862,13 +894,13 @@
       <c r="F14" t="s">
         <v>11</v>
       </c>
-      <c r="J14" s="8" t="s">
+      <c r="J14" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="K14" s="9" t="s">
+      <c r="K14" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="L14" s="10" t="s">
+      <c r="L14" s="7" t="s">
         <v>20</v>
       </c>
     </row>
@@ -876,11 +908,26 @@
       <c r="A15" s="4">
         <v>2</v>
       </c>
-      <c r="J15" s="11"/>
+      <c r="B15" t="s">
+        <v>4</v>
+      </c>
+      <c r="C15" t="s">
+        <v>56</v>
+      </c>
+      <c r="D15" t="s">
+        <v>57</v>
+      </c>
+      <c r="E15" t="s">
+        <v>11</v>
+      </c>
+      <c r="F15" t="s">
+        <v>11</v>
+      </c>
+      <c r="J15" s="8"/>
       <c r="K15" t="s">
         <v>21</v>
       </c>
-      <c r="L15" s="12" t="s">
+      <c r="L15" s="9" t="s">
         <v>22</v>
       </c>
     </row>
@@ -888,11 +935,11 @@
       <c r="A16" s="4">
         <v>3</v>
       </c>
-      <c r="J16" s="13"/>
+      <c r="J16" s="10"/>
       <c r="K16" t="s">
         <v>23</v>
       </c>
-      <c r="L16" s="12" t="s">
+      <c r="L16" s="9" t="s">
         <v>24</v>
       </c>
     </row>
@@ -900,11 +947,11 @@
       <c r="A17" s="4">
         <v>4</v>
       </c>
-      <c r="J17" s="14"/>
+      <c r="J17" s="11"/>
       <c r="K17" t="s">
         <v>25</v>
       </c>
-      <c r="L17" s="12" t="s">
+      <c r="L17" s="9" t="s">
         <v>24</v>
       </c>
     </row>
@@ -912,11 +959,11 @@
       <c r="A18" s="4">
         <v>5</v>
       </c>
-      <c r="J18" s="15"/>
-      <c r="K18" s="16" t="s">
+      <c r="J18" s="12"/>
+      <c r="K18" s="13" t="s">
         <v>26</v>
       </c>
-      <c r="L18" s="17" t="s">
+      <c r="L18" s="14" t="s">
         <v>22</v>
       </c>
     </row>
@@ -930,7 +977,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E58FD589-5976-4A3F-AC8C-971D910984C4}">
-  <dimension ref="A1:D10"/>
+  <dimension ref="A1:D13"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="37.44140625" bestFit="1" customWidth="1"/>
@@ -943,120 +990,156 @@
       <c r="B1" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="C1" s="22" t="s">
+      <c r="C1" s="18" t="s">
         <v>30</v>
       </c>
-      <c r="D1" s="18" t="s">
+      <c r="D1" s="3" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="2" spans="1:4" ht="15" thickTop="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="19" t="s">
+      <c r="A2" s="15" t="s">
         <v>12</v>
       </c>
       <c r="B2" t="s">
         <v>35</v>
       </c>
-      <c r="C2" s="23" t="s">
+      <c r="C2" s="19" t="s">
         <v>14</v>
       </c>
-      <c r="D2" s="21"/>
+      <c r="D2" s="17"/>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A3" s="19" t="s">
+      <c r="A3" s="15" t="s">
         <v>31</v>
       </c>
       <c r="B3" t="s">
         <v>37</v>
       </c>
-      <c r="C3" s="23" t="s">
+      <c r="C3" s="19" t="s">
         <v>14</v>
       </c>
-      <c r="D3" s="21"/>
+      <c r="D3" s="17"/>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A4" s="19" t="s">
+      <c r="A4" s="15" t="s">
         <v>13</v>
       </c>
       <c r="B4" t="s">
         <v>38</v>
       </c>
-      <c r="C4" s="23" t="s">
+      <c r="C4" s="19" t="s">
         <v>15</v>
       </c>
-      <c r="D4" s="21"/>
+      <c r="D4" s="17"/>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A5" s="20" t="s">
+      <c r="A5" s="16" t="s">
         <v>32</v>
       </c>
       <c r="B5" t="s">
         <v>39</v>
       </c>
-      <c r="C5" s="23" t="s">
+      <c r="C5" s="19" t="s">
         <v>36</v>
       </c>
-      <c r="D5" s="21"/>
+      <c r="D5" s="17"/>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A6" s="20" t="s">
+      <c r="A6" s="16" t="s">
         <v>33</v>
       </c>
       <c r="B6" t="s">
         <v>40</v>
       </c>
-      <c r="C6" s="23" t="s">
+      <c r="C6" s="19" t="s">
         <v>36</v>
       </c>
-      <c r="D6" s="21"/>
+      <c r="D6" s="17"/>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A7" s="20" t="s">
+      <c r="A7" s="16" t="s">
         <v>34</v>
       </c>
       <c r="B7" t="s">
+        <v>55</v>
+      </c>
+      <c r="C7" s="19" t="s">
+        <v>36</v>
+      </c>
+      <c r="D7" s="17"/>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A8" s="20" t="s">
         <v>41</v>
       </c>
-      <c r="C7" s="23" t="s">
+      <c r="B8" t="s">
+        <v>44</v>
+      </c>
+      <c r="C8" s="19" t="s">
         <v>36</v>
       </c>
-      <c r="D7" s="21"/>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A8" s="24" t="s">
+      <c r="D8" s="17"/>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A9" s="20" t="s">
         <v>42</v>
       </c>
-      <c r="B8" t="s">
+      <c r="B9" t="s">
         <v>45</v>
       </c>
-      <c r="C8" s="23" t="s">
+      <c r="C9" s="19" t="s">
         <v>36</v>
       </c>
-      <c r="D8" s="21"/>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A9" s="24" t="s">
+      <c r="D9" s="17"/>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A10" s="20" t="s">
         <v>43</v>
       </c>
-      <c r="B9" t="s">
-        <v>46</v>
-      </c>
-      <c r="C9" s="23" t="s">
+      <c r="B10" t="s">
+        <v>54</v>
+      </c>
+      <c r="C10" s="19" t="s">
         <v>36</v>
       </c>
-      <c r="D9" s="21"/>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A10" s="24" t="s">
-        <v>44</v>
-      </c>
-      <c r="B10" t="s">
-        <v>47</v>
-      </c>
-      <c r="C10" s="23" t="s">
+      <c r="D10" s="17"/>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A11" s="20" t="s">
+        <v>48</v>
+      </c>
+      <c r="B11" t="s">
+        <v>51</v>
+      </c>
+      <c r="C11" s="19" t="s">
         <v>36</v>
       </c>
-      <c r="D10" s="21"/>
+      <c r="D11" s="17"/>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A12" s="20" t="s">
+        <v>49</v>
+      </c>
+      <c r="B12" t="s">
+        <v>52</v>
+      </c>
+      <c r="C12" s="19" t="s">
+        <v>36</v>
+      </c>
+      <c r="D12" s="17"/>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A13" s="20" t="s">
+        <v>50</v>
+      </c>
+      <c r="B13" t="s">
+        <v>53</v>
+      </c>
+      <c r="C13" s="19" t="s">
+        <v>36</v>
+      </c>
+      <c r="D13" s="17"/>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
@@ -1067,68 +1150,86 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B17F5867-AD4D-437E-9587-013CCE57CB0D}">
-  <dimension ref="A1:I35"/>
+  <dimension ref="A1:L35"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A1" s="25" t="s">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A1" s="21" t="s">
         <v>12</v>
       </c>
-      <c r="B1" s="25" t="s">
+      <c r="B1" s="21" t="s">
         <v>31</v>
       </c>
-      <c r="C1" s="27" t="s">
+      <c r="C1" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="D1" s="29" t="s">
+      <c r="D1" s="25" t="s">
         <v>32</v>
       </c>
-      <c r="E1" s="29" t="s">
+      <c r="E1" s="25" t="s">
         <v>33</v>
       </c>
-      <c r="F1" s="30" t="s">
+      <c r="F1" s="26" t="s">
         <v>34</v>
       </c>
-      <c r="G1" s="29" t="s">
+      <c r="G1" s="32" t="s">
+        <v>41</v>
+      </c>
+      <c r="H1" s="33" t="s">
         <v>42</v>
       </c>
-      <c r="H1" s="29" t="s">
+      <c r="I1" s="26" t="s">
         <v>43</v>
       </c>
-      <c r="I1" s="29" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="2" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="26" t="s">
+      <c r="J1" s="25" t="s">
+        <v>48</v>
+      </c>
+      <c r="K1" s="25" t="s">
+        <v>49</v>
+      </c>
+      <c r="L1" s="25" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="22" t="s">
         <v>14</v>
       </c>
-      <c r="B2" s="26" t="s">
+      <c r="B2" s="22" t="s">
         <v>14</v>
       </c>
-      <c r="C2" s="28" t="s">
+      <c r="C2" s="24" t="s">
         <v>15</v>
       </c>
-      <c r="D2" s="31" t="s">
-        <v>48</v>
-      </c>
-      <c r="E2" s="31" t="s">
-        <v>48</v>
-      </c>
-      <c r="F2" s="32" t="s">
-        <v>48</v>
-      </c>
-      <c r="G2" s="31" t="s">
-        <v>49</v>
-      </c>
-      <c r="H2" s="31" t="s">
-        <v>49</v>
-      </c>
-      <c r="I2" s="31" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="3" spans="1:9" ht="15" thickTop="1" x14ac:dyDescent="0.3">
+      <c r="D2" s="27" t="s">
+        <v>46</v>
+      </c>
+      <c r="E2" s="27" t="s">
+        <v>46</v>
+      </c>
+      <c r="F2" s="28" t="s">
+        <v>46</v>
+      </c>
+      <c r="G2" s="34" t="s">
+        <v>47</v>
+      </c>
+      <c r="H2" s="27" t="s">
+        <v>47</v>
+      </c>
+      <c r="I2" s="28" t="s">
+        <v>47</v>
+      </c>
+      <c r="J2" s="27" t="s">
+        <v>47</v>
+      </c>
+      <c r="K2" s="27" t="s">
+        <v>47</v>
+      </c>
+      <c r="L2" s="27" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" ht="15" thickTop="1" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>0</v>
       </c>
@@ -1138,26 +1239,35 @@
       <c r="C3" s="4">
         <v>1</v>
       </c>
-      <c r="D3" s="33">
-        <v>0</v>
-      </c>
-      <c r="E3" s="33">
+      <c r="D3">
+        <v>0</v>
+      </c>
+      <c r="E3">
         <v>0</v>
       </c>
       <c r="F3" s="4">
         <v>0</v>
       </c>
-      <c r="G3" s="33">
-        <v>0</v>
-      </c>
-      <c r="H3" s="33">
-        <v>0</v>
-      </c>
-      <c r="I3" s="33">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="G3" s="19">
+        <v>0</v>
+      </c>
+      <c r="H3" s="35">
+        <v>0</v>
+      </c>
+      <c r="I3" s="4">
+        <v>0</v>
+      </c>
+      <c r="J3">
+        <v>0</v>
+      </c>
+      <c r="K3">
+        <v>0</v>
+      </c>
+      <c r="L3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>1</v>
       </c>
@@ -1167,26 +1277,35 @@
       <c r="C4" s="4">
         <v>1</v>
       </c>
-      <c r="D4" s="33">
-        <v>0</v>
-      </c>
-      <c r="E4" s="33">
+      <c r="D4">
+        <v>0</v>
+      </c>
+      <c r="E4">
         <v>0</v>
       </c>
       <c r="F4" s="4">
         <v>0</v>
       </c>
-      <c r="G4" s="33">
-        <v>0</v>
-      </c>
-      <c r="H4" s="33">
-        <v>0</v>
-      </c>
-      <c r="I4" s="33">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="G4" s="19">
+        <v>0</v>
+      </c>
+      <c r="H4" s="35">
+        <v>0</v>
+      </c>
+      <c r="I4" s="4">
+        <v>0</v>
+      </c>
+      <c r="J4">
+        <v>0</v>
+      </c>
+      <c r="K4">
+        <v>0</v>
+      </c>
+      <c r="L4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>2</v>
       </c>
@@ -1196,26 +1315,35 @@
       <c r="C5" s="4">
         <v>1</v>
       </c>
-      <c r="D5" s="33">
-        <v>0</v>
-      </c>
-      <c r="E5" s="33">
+      <c r="D5">
+        <v>0</v>
+      </c>
+      <c r="E5">
         <v>0</v>
       </c>
       <c r="F5" s="4">
         <v>0</v>
       </c>
-      <c r="G5" s="33">
-        <v>0</v>
-      </c>
-      <c r="H5" s="33">
-        <v>0</v>
-      </c>
-      <c r="I5" s="33">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="G5" s="19">
+        <v>0</v>
+      </c>
+      <c r="H5" s="35">
+        <v>0</v>
+      </c>
+      <c r="I5" s="4">
+        <v>0</v>
+      </c>
+      <c r="J5">
+        <v>0</v>
+      </c>
+      <c r="K5">
+        <v>0</v>
+      </c>
+      <c r="L5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>3</v>
       </c>
@@ -1225,26 +1353,35 @@
       <c r="C6" s="4">
         <v>1</v>
       </c>
-      <c r="D6" s="33">
-        <v>0</v>
-      </c>
-      <c r="E6" s="33">
+      <c r="D6">
+        <v>0</v>
+      </c>
+      <c r="E6">
         <v>0</v>
       </c>
       <c r="F6" s="4">
         <v>0</v>
       </c>
-      <c r="G6" s="33">
-        <v>0</v>
-      </c>
-      <c r="H6" s="33">
-        <v>0</v>
-      </c>
-      <c r="I6" s="33">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="G6" s="19">
+        <v>0</v>
+      </c>
+      <c r="H6" s="35">
+        <v>0</v>
+      </c>
+      <c r="I6" s="4">
+        <v>0</v>
+      </c>
+      <c r="J6">
+        <v>0</v>
+      </c>
+      <c r="K6">
+        <v>0</v>
+      </c>
+      <c r="L6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>4</v>
       </c>
@@ -1254,26 +1391,35 @@
       <c r="C7" s="4">
         <v>1</v>
       </c>
-      <c r="D7" s="33">
-        <v>0</v>
-      </c>
-      <c r="E7" s="33">
+      <c r="D7">
+        <v>0</v>
+      </c>
+      <c r="E7">
         <v>0</v>
       </c>
       <c r="F7" s="4">
         <v>0</v>
       </c>
-      <c r="G7" s="33">
-        <v>0</v>
-      </c>
-      <c r="H7" s="33">
-        <v>0</v>
-      </c>
-      <c r="I7" s="33">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="G7" s="19">
+        <v>0</v>
+      </c>
+      <c r="H7" s="35">
+        <v>0</v>
+      </c>
+      <c r="I7" s="4">
+        <v>0</v>
+      </c>
+      <c r="J7">
+        <v>0</v>
+      </c>
+      <c r="K7">
+        <v>0</v>
+      </c>
+      <c r="L7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>5</v>
       </c>
@@ -1283,26 +1429,35 @@
       <c r="C8" s="4">
         <v>1</v>
       </c>
-      <c r="D8" s="33">
-        <v>0</v>
-      </c>
-      <c r="E8" s="33">
+      <c r="D8">
+        <v>0</v>
+      </c>
+      <c r="E8">
         <v>0</v>
       </c>
       <c r="F8" s="4">
         <v>0</v>
       </c>
-      <c r="G8" s="33">
-        <v>0</v>
-      </c>
-      <c r="H8" s="33">
-        <v>0</v>
-      </c>
-      <c r="I8" s="33">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="G8" s="19">
+        <v>0</v>
+      </c>
+      <c r="H8" s="35">
+        <v>0</v>
+      </c>
+      <c r="I8" s="4">
+        <v>0</v>
+      </c>
+      <c r="J8">
+        <v>0</v>
+      </c>
+      <c r="K8">
+        <v>0</v>
+      </c>
+      <c r="L8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>6</v>
       </c>
@@ -1312,26 +1467,35 @@
       <c r="C9" s="4">
         <v>1</v>
       </c>
-      <c r="D9" s="33">
-        <v>0</v>
-      </c>
-      <c r="E9" s="33">
+      <c r="D9">
+        <v>0</v>
+      </c>
+      <c r="E9">
         <v>0</v>
       </c>
       <c r="F9" s="4">
         <v>0</v>
       </c>
-      <c r="G9" s="33">
-        <v>0</v>
-      </c>
-      <c r="H9" s="33">
-        <v>0</v>
-      </c>
-      <c r="I9" s="33">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="G9" s="19">
+        <v>0</v>
+      </c>
+      <c r="H9" s="35">
+        <v>0</v>
+      </c>
+      <c r="I9" s="4">
+        <v>0</v>
+      </c>
+      <c r="J9">
+        <v>0</v>
+      </c>
+      <c r="K9">
+        <v>0</v>
+      </c>
+      <c r="L9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>7</v>
       </c>
@@ -1341,26 +1505,35 @@
       <c r="C10" s="4">
         <v>1</v>
       </c>
-      <c r="D10" s="33">
-        <v>0</v>
-      </c>
-      <c r="E10" s="33">
+      <c r="D10">
+        <v>0</v>
+      </c>
+      <c r="E10">
         <v>0</v>
       </c>
       <c r="F10" s="4">
         <v>0</v>
       </c>
-      <c r="G10" s="33">
-        <v>0</v>
-      </c>
-      <c r="H10" s="33">
-        <v>0</v>
-      </c>
-      <c r="I10" s="33">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="G10" s="19">
+        <v>0</v>
+      </c>
+      <c r="H10" s="35">
+        <v>0</v>
+      </c>
+      <c r="I10" s="4">
+        <v>0</v>
+      </c>
+      <c r="J10">
+        <v>0</v>
+      </c>
+      <c r="K10">
+        <v>0</v>
+      </c>
+      <c r="L10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>8</v>
       </c>
@@ -1370,26 +1543,35 @@
       <c r="C11" s="4">
         <v>1</v>
       </c>
-      <c r="D11" s="33">
-        <v>0</v>
-      </c>
-      <c r="E11" s="33">
+      <c r="D11">
+        <v>0</v>
+      </c>
+      <c r="E11">
         <v>0</v>
       </c>
       <c r="F11" s="4">
         <v>0</v>
       </c>
-      <c r="G11" s="33">
-        <v>0</v>
-      </c>
-      <c r="H11" s="33">
-        <v>0</v>
-      </c>
-      <c r="I11" s="33">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="G11" s="19">
+        <v>0</v>
+      </c>
+      <c r="H11" s="35">
+        <v>0</v>
+      </c>
+      <c r="I11" s="4">
+        <v>0</v>
+      </c>
+      <c r="J11">
+        <v>0</v>
+      </c>
+      <c r="K11">
+        <v>0</v>
+      </c>
+      <c r="L11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>9</v>
       </c>
@@ -1399,26 +1581,35 @@
       <c r="C12" s="4">
         <v>1</v>
       </c>
-      <c r="D12" s="33">
-        <v>0</v>
-      </c>
-      <c r="E12" s="33">
+      <c r="D12">
+        <v>0</v>
+      </c>
+      <c r="E12">
         <v>0</v>
       </c>
       <c r="F12" s="4">
         <v>0</v>
       </c>
-      <c r="G12" s="33">
-        <v>0</v>
-      </c>
-      <c r="H12" s="33">
-        <v>0</v>
-      </c>
-      <c r="I12" s="33">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="G12" s="19">
+        <v>0</v>
+      </c>
+      <c r="H12" s="35">
+        <v>0</v>
+      </c>
+      <c r="I12" s="4">
+        <v>0</v>
+      </c>
+      <c r="J12">
+        <v>0</v>
+      </c>
+      <c r="K12">
+        <v>0</v>
+      </c>
+      <c r="L12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>10</v>
       </c>
@@ -1428,26 +1619,35 @@
       <c r="C13" s="4">
         <v>1</v>
       </c>
-      <c r="D13" s="33">
-        <v>0</v>
-      </c>
-      <c r="E13" s="33">
+      <c r="D13">
+        <v>0</v>
+      </c>
+      <c r="E13">
         <v>0</v>
       </c>
       <c r="F13" s="4">
         <v>0</v>
       </c>
-      <c r="G13" s="33">
-        <v>0</v>
-      </c>
-      <c r="H13" s="33">
-        <v>0</v>
-      </c>
-      <c r="I13" s="33">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="G13" s="19">
+        <v>0</v>
+      </c>
+      <c r="H13" s="35">
+        <v>0</v>
+      </c>
+      <c r="I13" s="4">
+        <v>0</v>
+      </c>
+      <c r="J13">
+        <v>0</v>
+      </c>
+      <c r="K13">
+        <v>0</v>
+      </c>
+      <c r="L13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>11</v>
       </c>
@@ -1457,26 +1657,35 @@
       <c r="C14" s="4">
         <v>2</v>
       </c>
-      <c r="D14" s="33">
-        <v>0</v>
-      </c>
-      <c r="E14" s="33">
+      <c r="D14">
+        <v>0</v>
+      </c>
+      <c r="E14">
         <v>0</v>
       </c>
       <c r="F14" s="4">
         <v>0</v>
       </c>
-      <c r="G14" s="33">
-        <v>0</v>
-      </c>
-      <c r="H14" s="33">
-        <v>0</v>
-      </c>
-      <c r="I14" s="33">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="G14" s="19">
+        <v>0</v>
+      </c>
+      <c r="H14" s="35">
+        <v>0</v>
+      </c>
+      <c r="I14" s="4">
+        <v>0</v>
+      </c>
+      <c r="J14">
+        <v>0</v>
+      </c>
+      <c r="K14">
+        <v>0</v>
+      </c>
+      <c r="L14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A15">
         <v>12</v>
       </c>
@@ -1486,26 +1695,35 @@
       <c r="C15" s="4">
         <v>2</v>
       </c>
-      <c r="D15" s="33">
-        <v>0</v>
-      </c>
-      <c r="E15" s="33">
+      <c r="D15">
+        <v>0</v>
+      </c>
+      <c r="E15">
         <v>0</v>
       </c>
       <c r="F15" s="4">
         <v>0</v>
       </c>
-      <c r="G15" s="33">
-        <v>0</v>
-      </c>
-      <c r="H15" s="33">
-        <v>0</v>
-      </c>
-      <c r="I15" s="33">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="G15" s="19">
+        <v>0</v>
+      </c>
+      <c r="H15" s="35">
+        <v>0</v>
+      </c>
+      <c r="I15" s="4">
+        <v>0</v>
+      </c>
+      <c r="J15">
+        <v>0</v>
+      </c>
+      <c r="K15">
+        <v>0</v>
+      </c>
+      <c r="L15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A16">
         <v>13</v>
       </c>
@@ -1515,26 +1733,35 @@
       <c r="C16" s="4">
         <v>2</v>
       </c>
-      <c r="D16" s="33">
-        <v>0</v>
-      </c>
-      <c r="E16" s="33">
+      <c r="D16">
+        <v>0</v>
+      </c>
+      <c r="E16">
         <v>0</v>
       </c>
       <c r="F16" s="4">
         <v>0</v>
       </c>
-      <c r="G16" s="33">
-        <v>0</v>
-      </c>
-      <c r="H16" s="33">
-        <v>0</v>
-      </c>
-      <c r="I16" s="33">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="G16" s="19">
+        <v>0</v>
+      </c>
+      <c r="H16" s="35">
+        <v>0</v>
+      </c>
+      <c r="I16" s="4">
+        <v>0</v>
+      </c>
+      <c r="J16">
+        <v>0</v>
+      </c>
+      <c r="K16">
+        <v>0</v>
+      </c>
+      <c r="L16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A17">
         <v>14</v>
       </c>
@@ -1544,26 +1771,35 @@
       <c r="C17" s="4">
         <v>2</v>
       </c>
-      <c r="D17" s="33">
-        <v>0</v>
-      </c>
-      <c r="E17" s="33">
+      <c r="D17">
+        <v>0</v>
+      </c>
+      <c r="E17">
         <v>0</v>
       </c>
       <c r="F17" s="4">
         <v>0</v>
       </c>
-      <c r="G17" s="33">
-        <v>0</v>
-      </c>
-      <c r="H17" s="33">
-        <v>0</v>
-      </c>
-      <c r="I17" s="33">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="G17" s="19">
+        <v>0</v>
+      </c>
+      <c r="H17" s="35">
+        <v>0</v>
+      </c>
+      <c r="I17" s="4">
+        <v>0</v>
+      </c>
+      <c r="J17">
+        <v>0</v>
+      </c>
+      <c r="K17">
+        <v>0</v>
+      </c>
+      <c r="L17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A18">
         <v>15</v>
       </c>
@@ -1573,26 +1809,35 @@
       <c r="C18" s="4">
         <v>2</v>
       </c>
-      <c r="D18" s="33">
-        <v>0</v>
-      </c>
-      <c r="E18" s="33">
+      <c r="D18">
+        <v>0</v>
+      </c>
+      <c r="E18">
         <v>0</v>
       </c>
       <c r="F18" s="4">
         <v>0</v>
       </c>
-      <c r="G18" s="33">
-        <v>0</v>
-      </c>
-      <c r="H18" s="33">
-        <v>0</v>
-      </c>
-      <c r="I18" s="33">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="G18" s="19">
+        <v>0</v>
+      </c>
+      <c r="H18" s="35">
+        <v>0</v>
+      </c>
+      <c r="I18" s="4">
+        <v>0</v>
+      </c>
+      <c r="J18">
+        <v>0</v>
+      </c>
+      <c r="K18">
+        <v>0</v>
+      </c>
+      <c r="L18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A19">
         <v>16</v>
       </c>
@@ -1602,26 +1847,35 @@
       <c r="C19" s="4">
         <v>2</v>
       </c>
-      <c r="D19" s="33">
-        <v>0</v>
-      </c>
-      <c r="E19" s="33">
+      <c r="D19">
+        <v>0</v>
+      </c>
+      <c r="E19">
         <v>0</v>
       </c>
       <c r="F19" s="4">
         <v>0</v>
       </c>
-      <c r="G19" s="33">
-        <v>0</v>
-      </c>
-      <c r="H19" s="33">
-        <v>0</v>
-      </c>
-      <c r="I19" s="33">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="G19" s="19">
+        <v>0</v>
+      </c>
+      <c r="H19" s="35">
+        <v>0</v>
+      </c>
+      <c r="I19" s="4">
+        <v>0</v>
+      </c>
+      <c r="J19">
+        <v>0</v>
+      </c>
+      <c r="K19">
+        <v>0</v>
+      </c>
+      <c r="L19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A20">
         <v>17</v>
       </c>
@@ -1631,26 +1885,35 @@
       <c r="C20" s="4">
         <v>2</v>
       </c>
-      <c r="D20" s="33">
-        <v>0</v>
-      </c>
-      <c r="E20" s="33">
+      <c r="D20">
+        <v>0</v>
+      </c>
+      <c r="E20">
         <v>0</v>
       </c>
       <c r="F20" s="4">
         <v>0</v>
       </c>
-      <c r="G20" s="33">
-        <v>0</v>
-      </c>
-      <c r="H20" s="33">
-        <v>0</v>
-      </c>
-      <c r="I20" s="33">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="G20" s="19">
+        <v>0</v>
+      </c>
+      <c r="H20" s="35">
+        <v>0</v>
+      </c>
+      <c r="I20" s="4">
+        <v>0</v>
+      </c>
+      <c r="J20">
+        <v>0</v>
+      </c>
+      <c r="K20">
+        <v>0</v>
+      </c>
+      <c r="L20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A21">
         <v>18</v>
       </c>
@@ -1660,26 +1923,35 @@
       <c r="C21" s="4">
         <v>2</v>
       </c>
-      <c r="D21" s="33">
-        <v>0</v>
-      </c>
-      <c r="E21" s="33">
+      <c r="D21">
+        <v>0</v>
+      </c>
+      <c r="E21">
         <v>0</v>
       </c>
       <c r="F21" s="4">
         <v>0</v>
       </c>
-      <c r="G21" s="33">
-        <v>0</v>
-      </c>
-      <c r="H21" s="33">
-        <v>0</v>
-      </c>
-      <c r="I21" s="33">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="G21" s="19">
+        <v>0</v>
+      </c>
+      <c r="H21" s="35">
+        <v>0</v>
+      </c>
+      <c r="I21" s="4">
+        <v>0</v>
+      </c>
+      <c r="J21">
+        <v>0</v>
+      </c>
+      <c r="K21">
+        <v>0</v>
+      </c>
+      <c r="L21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A22">
         <v>19</v>
       </c>
@@ -1689,26 +1961,35 @@
       <c r="C22" s="4">
         <v>2</v>
       </c>
-      <c r="D22" s="33">
-        <v>0</v>
-      </c>
-      <c r="E22" s="33">
+      <c r="D22">
+        <v>0</v>
+      </c>
+      <c r="E22">
         <v>0</v>
       </c>
       <c r="F22" s="4">
         <v>0</v>
       </c>
-      <c r="G22" s="33">
-        <v>0</v>
-      </c>
-      <c r="H22" s="33">
-        <v>0</v>
-      </c>
-      <c r="I22" s="33">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="G22" s="19">
+        <v>0</v>
+      </c>
+      <c r="H22" s="35">
+        <v>0</v>
+      </c>
+      <c r="I22" s="4">
+        <v>0</v>
+      </c>
+      <c r="J22">
+        <v>0</v>
+      </c>
+      <c r="K22">
+        <v>0</v>
+      </c>
+      <c r="L22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A23">
         <v>20</v>
       </c>
@@ -1718,26 +1999,35 @@
       <c r="C23" s="4">
         <v>2</v>
       </c>
-      <c r="D23" s="33">
-        <v>0</v>
-      </c>
-      <c r="E23" s="33">
+      <c r="D23">
+        <v>0</v>
+      </c>
+      <c r="E23">
         <v>0</v>
       </c>
       <c r="F23" s="4">
         <v>0</v>
       </c>
-      <c r="G23" s="33">
-        <v>0</v>
-      </c>
-      <c r="H23" s="33">
-        <v>0</v>
-      </c>
-      <c r="I23" s="33">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="G23" s="19">
+        <v>0</v>
+      </c>
+      <c r="H23" s="35">
+        <v>0</v>
+      </c>
+      <c r="I23" s="4">
+        <v>0</v>
+      </c>
+      <c r="J23">
+        <v>0</v>
+      </c>
+      <c r="K23">
+        <v>0</v>
+      </c>
+      <c r="L23">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A24">
         <v>21</v>
       </c>
@@ -1747,26 +2037,35 @@
       <c r="C24" s="4">
         <v>2</v>
       </c>
-      <c r="D24" s="33">
-        <v>0</v>
-      </c>
-      <c r="E24" s="33">
+      <c r="D24">
+        <v>0</v>
+      </c>
+      <c r="E24">
         <v>0</v>
       </c>
       <c r="F24" s="4">
         <v>0</v>
       </c>
-      <c r="G24" s="33">
-        <v>0</v>
-      </c>
-      <c r="H24" s="33">
-        <v>0</v>
-      </c>
-      <c r="I24" s="33">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="G24" s="19">
+        <v>0</v>
+      </c>
+      <c r="H24" s="35">
+        <v>0</v>
+      </c>
+      <c r="I24" s="4">
+        <v>0</v>
+      </c>
+      <c r="J24">
+        <v>0</v>
+      </c>
+      <c r="K24">
+        <v>0</v>
+      </c>
+      <c r="L24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A25">
         <v>22</v>
       </c>
@@ -1776,26 +2075,35 @@
       <c r="C25" s="4">
         <v>3</v>
       </c>
-      <c r="D25" s="33">
-        <v>0</v>
-      </c>
-      <c r="E25" s="33">
+      <c r="D25">
+        <v>0</v>
+      </c>
+      <c r="E25">
         <v>0</v>
       </c>
       <c r="F25" s="4">
         <v>0</v>
       </c>
-      <c r="G25" s="33">
-        <v>0</v>
-      </c>
-      <c r="H25" s="33">
-        <v>0</v>
-      </c>
-      <c r="I25" s="33">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="G25" s="19">
+        <v>0</v>
+      </c>
+      <c r="H25" s="35">
+        <v>0</v>
+      </c>
+      <c r="I25" s="4">
+        <v>0</v>
+      </c>
+      <c r="J25">
+        <v>0</v>
+      </c>
+      <c r="K25">
+        <v>0</v>
+      </c>
+      <c r="L25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A26">
         <v>23</v>
       </c>
@@ -1805,26 +2113,35 @@
       <c r="C26" s="4">
         <v>3</v>
       </c>
-      <c r="D26" s="33">
-        <v>0</v>
-      </c>
-      <c r="E26" s="33">
+      <c r="D26">
+        <v>0</v>
+      </c>
+      <c r="E26">
         <v>0</v>
       </c>
       <c r="F26" s="4">
         <v>0</v>
       </c>
-      <c r="G26" s="33">
-        <v>0</v>
-      </c>
-      <c r="H26" s="33">
-        <v>0</v>
-      </c>
-      <c r="I26" s="33">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="G26" s="19">
+        <v>0</v>
+      </c>
+      <c r="H26" s="35">
+        <v>0</v>
+      </c>
+      <c r="I26" s="4">
+        <v>0</v>
+      </c>
+      <c r="J26">
+        <v>0</v>
+      </c>
+      <c r="K26">
+        <v>0</v>
+      </c>
+      <c r="L26">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A27">
         <v>24</v>
       </c>
@@ -1834,26 +2151,35 @@
       <c r="C27" s="4">
         <v>3</v>
       </c>
-      <c r="D27" s="33">
-        <v>0</v>
-      </c>
-      <c r="E27" s="33">
+      <c r="D27">
+        <v>0</v>
+      </c>
+      <c r="E27">
         <v>0</v>
       </c>
       <c r="F27" s="4">
         <v>0</v>
       </c>
-      <c r="G27" s="33">
-        <v>0</v>
-      </c>
-      <c r="H27" s="33">
-        <v>0</v>
-      </c>
-      <c r="I27" s="33">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="G27" s="19">
+        <v>0</v>
+      </c>
+      <c r="H27" s="35">
+        <v>0</v>
+      </c>
+      <c r="I27" s="4">
+        <v>0</v>
+      </c>
+      <c r="J27">
+        <v>0</v>
+      </c>
+      <c r="K27">
+        <v>0</v>
+      </c>
+      <c r="L27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A28">
         <v>25</v>
       </c>
@@ -1863,26 +2189,35 @@
       <c r="C28" s="4">
         <v>3</v>
       </c>
-      <c r="D28" s="33">
-        <v>0</v>
-      </c>
-      <c r="E28" s="33">
+      <c r="D28">
+        <v>0</v>
+      </c>
+      <c r="E28">
         <v>0</v>
       </c>
       <c r="F28" s="4">
         <v>0</v>
       </c>
-      <c r="G28" s="33">
-        <v>0</v>
-      </c>
-      <c r="H28" s="33">
-        <v>0</v>
-      </c>
-      <c r="I28" s="33">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="G28" s="19">
+        <v>0</v>
+      </c>
+      <c r="H28" s="35">
+        <v>0</v>
+      </c>
+      <c r="I28" s="4">
+        <v>0</v>
+      </c>
+      <c r="J28">
+        <v>0</v>
+      </c>
+      <c r="K28">
+        <v>0</v>
+      </c>
+      <c r="L28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A29">
         <v>26</v>
       </c>
@@ -1892,26 +2227,35 @@
       <c r="C29" s="4">
         <v>3</v>
       </c>
-      <c r="D29" s="33">
-        <v>0</v>
-      </c>
-      <c r="E29" s="33">
+      <c r="D29">
+        <v>0</v>
+      </c>
+      <c r="E29">
         <v>0</v>
       </c>
       <c r="F29" s="4">
         <v>0</v>
       </c>
-      <c r="G29" s="33">
-        <v>0</v>
-      </c>
-      <c r="H29" s="33">
-        <v>0</v>
-      </c>
-      <c r="I29" s="33">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="G29" s="19">
+        <v>0</v>
+      </c>
+      <c r="H29" s="35">
+        <v>0</v>
+      </c>
+      <c r="I29" s="4">
+        <v>0</v>
+      </c>
+      <c r="J29">
+        <v>0</v>
+      </c>
+      <c r="K29">
+        <v>0</v>
+      </c>
+      <c r="L29">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A30">
         <v>27</v>
       </c>
@@ -1921,26 +2265,35 @@
       <c r="C30" s="4">
         <v>3</v>
       </c>
-      <c r="D30" s="33">
-        <v>0</v>
-      </c>
-      <c r="E30" s="33">
+      <c r="D30">
+        <v>0</v>
+      </c>
+      <c r="E30">
         <v>0</v>
       </c>
       <c r="F30" s="4">
         <v>0</v>
       </c>
-      <c r="G30" s="33">
-        <v>0</v>
-      </c>
-      <c r="H30" s="33">
-        <v>0</v>
-      </c>
-      <c r="I30" s="33">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="31" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="G30" s="19">
+        <v>0</v>
+      </c>
+      <c r="H30" s="35">
+        <v>0</v>
+      </c>
+      <c r="I30" s="4">
+        <v>0</v>
+      </c>
+      <c r="J30">
+        <v>0</v>
+      </c>
+      <c r="K30">
+        <v>0</v>
+      </c>
+      <c r="L30">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A31">
         <v>28</v>
       </c>
@@ -1950,26 +2303,35 @@
       <c r="C31" s="4">
         <v>3</v>
       </c>
-      <c r="D31" s="33">
-        <v>0</v>
-      </c>
-      <c r="E31" s="33">
+      <c r="D31">
+        <v>0</v>
+      </c>
+      <c r="E31">
         <v>0</v>
       </c>
       <c r="F31" s="4">
         <v>0</v>
       </c>
-      <c r="G31" s="33">
-        <v>0</v>
-      </c>
-      <c r="H31" s="33">
-        <v>0</v>
-      </c>
-      <c r="I31" s="33">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="32" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="G31" s="19">
+        <v>0</v>
+      </c>
+      <c r="H31" s="35">
+        <v>0</v>
+      </c>
+      <c r="I31" s="4">
+        <v>0</v>
+      </c>
+      <c r="J31">
+        <v>0</v>
+      </c>
+      <c r="K31">
+        <v>0</v>
+      </c>
+      <c r="L31">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A32">
         <v>29</v>
       </c>
@@ -1979,26 +2341,35 @@
       <c r="C32" s="4">
         <v>3</v>
       </c>
-      <c r="D32" s="33">
-        <v>0</v>
-      </c>
-      <c r="E32" s="33">
+      <c r="D32">
+        <v>0</v>
+      </c>
+      <c r="E32">
         <v>0</v>
       </c>
       <c r="F32" s="4">
         <v>0</v>
       </c>
-      <c r="G32" s="33">
-        <v>0</v>
-      </c>
-      <c r="H32" s="33">
-        <v>0</v>
-      </c>
-      <c r="I32" s="33">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="33" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="G32" s="19">
+        <v>0</v>
+      </c>
+      <c r="H32" s="35">
+        <v>0</v>
+      </c>
+      <c r="I32" s="4">
+        <v>0</v>
+      </c>
+      <c r="J32">
+        <v>0</v>
+      </c>
+      <c r="K32">
+        <v>0</v>
+      </c>
+      <c r="L32">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A33">
         <v>30</v>
       </c>
@@ -2008,26 +2379,35 @@
       <c r="C33" s="4">
         <v>3</v>
       </c>
-      <c r="D33" s="33">
-        <v>0</v>
-      </c>
-      <c r="E33" s="33">
+      <c r="D33">
+        <v>0</v>
+      </c>
+      <c r="E33">
         <v>0</v>
       </c>
       <c r="F33" s="4">
         <v>0</v>
       </c>
-      <c r="G33" s="33">
-        <v>0</v>
-      </c>
-      <c r="H33" s="33">
-        <v>0</v>
-      </c>
-      <c r="I33" s="33">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="34" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="G33" s="19">
+        <v>0</v>
+      </c>
+      <c r="H33" s="35">
+        <v>0</v>
+      </c>
+      <c r="I33" s="4">
+        <v>0</v>
+      </c>
+      <c r="J33">
+        <v>0</v>
+      </c>
+      <c r="K33">
+        <v>0</v>
+      </c>
+      <c r="L33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A34">
         <v>31</v>
       </c>
@@ -2037,26 +2417,35 @@
       <c r="C34" s="4">
         <v>3</v>
       </c>
-      <c r="D34" s="33">
-        <v>0</v>
-      </c>
-      <c r="E34" s="33">
+      <c r="D34">
+        <v>0</v>
+      </c>
+      <c r="E34">
         <v>0</v>
       </c>
       <c r="F34" s="4">
         <v>0</v>
       </c>
-      <c r="G34" s="33">
-        <v>0</v>
-      </c>
-      <c r="H34" s="33">
-        <v>0</v>
-      </c>
-      <c r="I34" s="33">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="35" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="G34" s="19">
+        <v>0</v>
+      </c>
+      <c r="H34" s="35">
+        <v>0</v>
+      </c>
+      <c r="I34" s="4">
+        <v>0</v>
+      </c>
+      <c r="J34">
+        <v>0</v>
+      </c>
+      <c r="K34">
+        <v>0</v>
+      </c>
+      <c r="L34">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A35">
         <v>32</v>
       </c>
@@ -2066,22 +2455,31 @@
       <c r="C35" s="4">
         <v>3</v>
       </c>
-      <c r="D35" s="33">
-        <v>0</v>
-      </c>
-      <c r="E35" s="33">
+      <c r="D35">
+        <v>0</v>
+      </c>
+      <c r="E35">
         <v>0</v>
       </c>
       <c r="F35" s="4">
         <v>0</v>
       </c>
-      <c r="G35" s="33">
-        <v>0</v>
-      </c>
-      <c r="H35" s="33">
-        <v>0</v>
-      </c>
-      <c r="I35" s="33">
+      <c r="G35" s="19">
+        <v>0</v>
+      </c>
+      <c r="H35" s="35">
+        <v>0</v>
+      </c>
+      <c r="I35" s="4">
+        <v>0</v>
+      </c>
+      <c r="J35">
+        <v>0</v>
+      </c>
+      <c r="K35">
+        <v>0</v>
+      </c>
+      <c r="L35">
         <v>0</v>
       </c>
     </row>
@@ -2093,68 +2491,86 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FE114676-A367-4C82-8117-B1844C4B2DB2}">
-  <dimension ref="A1:I35"/>
+  <dimension ref="A1:L35"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A1" s="25" t="s">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A1" s="21" t="s">
         <v>12</v>
       </c>
-      <c r="B1" s="25" t="s">
+      <c r="B1" s="21" t="s">
         <v>31</v>
       </c>
-      <c r="C1" s="27" t="s">
+      <c r="C1" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="D1" s="29" t="s">
+      <c r="D1" s="25" t="s">
         <v>32</v>
       </c>
-      <c r="E1" s="29" t="s">
+      <c r="E1" s="25" t="s">
         <v>33</v>
       </c>
-      <c r="F1" s="30" t="s">
+      <c r="F1" s="26" t="s">
         <v>34</v>
       </c>
-      <c r="G1" s="29" t="s">
+      <c r="G1" s="25" t="s">
+        <v>41</v>
+      </c>
+      <c r="H1" s="25" t="s">
         <v>42</v>
       </c>
-      <c r="H1" s="29" t="s">
+      <c r="I1" s="26" t="s">
         <v>43</v>
       </c>
-      <c r="I1" s="29" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="2" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="26" t="s">
+      <c r="J1" s="25" t="s">
+        <v>48</v>
+      </c>
+      <c r="K1" s="25" t="s">
+        <v>49</v>
+      </c>
+      <c r="L1" s="25" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="22" t="s">
         <v>14</v>
       </c>
-      <c r="B2" s="26" t="s">
+      <c r="B2" s="22" t="s">
         <v>14</v>
       </c>
-      <c r="C2" s="28" t="s">
+      <c r="C2" s="24" t="s">
         <v>15</v>
       </c>
-      <c r="D2" s="31" t="s">
-        <v>48</v>
-      </c>
-      <c r="E2" s="31" t="s">
-        <v>48</v>
-      </c>
-      <c r="F2" s="32" t="s">
-        <v>48</v>
-      </c>
-      <c r="G2" s="31" t="s">
-        <v>49</v>
-      </c>
-      <c r="H2" s="31" t="s">
-        <v>49</v>
-      </c>
-      <c r="I2" s="31" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="3" spans="1:9" ht="15" thickTop="1" x14ac:dyDescent="0.3">
+      <c r="D2" s="27" t="s">
+        <v>46</v>
+      </c>
+      <c r="E2" s="27" t="s">
+        <v>46</v>
+      </c>
+      <c r="F2" s="28" t="s">
+        <v>46</v>
+      </c>
+      <c r="G2" s="27" t="s">
+        <v>47</v>
+      </c>
+      <c r="H2" s="27" t="s">
+        <v>47</v>
+      </c>
+      <c r="I2" s="28" t="s">
+        <v>47</v>
+      </c>
+      <c r="J2" s="27" t="s">
+        <v>47</v>
+      </c>
+      <c r="K2" s="27" t="s">
+        <v>47</v>
+      </c>
+      <c r="L2" s="27" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" ht="15" thickTop="1" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>0</v>
       </c>
@@ -2164,26 +2580,35 @@
       <c r="C3" s="4">
         <v>1</v>
       </c>
-      <c r="D3" s="33">
-        <v>0</v>
-      </c>
-      <c r="E3" s="33">
+      <c r="D3">
+        <v>0</v>
+      </c>
+      <c r="E3">
         <v>0</v>
       </c>
       <c r="F3" s="4">
         <v>0</v>
       </c>
-      <c r="G3" s="33">
-        <v>0</v>
-      </c>
-      <c r="H3" s="33">
-        <v>0</v>
-      </c>
-      <c r="I3" s="33">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="G3">
+        <v>0</v>
+      </c>
+      <c r="H3">
+        <v>0</v>
+      </c>
+      <c r="I3" s="4">
+        <v>0</v>
+      </c>
+      <c r="J3">
+        <v>0</v>
+      </c>
+      <c r="K3">
+        <v>0</v>
+      </c>
+      <c r="L3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>1</v>
       </c>
@@ -2193,26 +2618,35 @@
       <c r="C4" s="4">
         <v>1</v>
       </c>
-      <c r="D4" s="33">
-        <v>0</v>
-      </c>
-      <c r="E4" s="33">
+      <c r="D4">
+        <v>0</v>
+      </c>
+      <c r="E4">
         <v>0</v>
       </c>
       <c r="F4" s="4">
         <v>0</v>
       </c>
-      <c r="G4" s="33">
-        <v>0</v>
-      </c>
-      <c r="H4" s="33">
-        <v>0</v>
-      </c>
-      <c r="I4" s="33">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="G4">
+        <v>0</v>
+      </c>
+      <c r="H4">
+        <v>0</v>
+      </c>
+      <c r="I4" s="4">
+        <v>0</v>
+      </c>
+      <c r="J4">
+        <v>0</v>
+      </c>
+      <c r="K4">
+        <v>0</v>
+      </c>
+      <c r="L4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>2</v>
       </c>
@@ -2222,26 +2656,35 @@
       <c r="C5" s="4">
         <v>1</v>
       </c>
-      <c r="D5" s="33">
-        <v>0</v>
-      </c>
-      <c r="E5" s="33">
+      <c r="D5">
+        <v>0</v>
+      </c>
+      <c r="E5">
         <v>0</v>
       </c>
       <c r="F5" s="4">
         <v>0</v>
       </c>
-      <c r="G5" s="33">
-        <v>0</v>
-      </c>
-      <c r="H5" s="33">
-        <v>0</v>
-      </c>
-      <c r="I5" s="33">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="G5">
+        <v>0</v>
+      </c>
+      <c r="H5">
+        <v>0</v>
+      </c>
+      <c r="I5" s="4">
+        <v>0</v>
+      </c>
+      <c r="J5">
+        <v>0</v>
+      </c>
+      <c r="K5">
+        <v>0</v>
+      </c>
+      <c r="L5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>3</v>
       </c>
@@ -2251,26 +2694,35 @@
       <c r="C6" s="4">
         <v>1</v>
       </c>
-      <c r="D6" s="33">
-        <v>0</v>
-      </c>
-      <c r="E6" s="33">
+      <c r="D6">
+        <v>0</v>
+      </c>
+      <c r="E6">
         <v>0</v>
       </c>
       <c r="F6" s="4">
         <v>0</v>
       </c>
-      <c r="G6" s="33">
-        <v>0</v>
-      </c>
-      <c r="H6" s="33">
-        <v>0</v>
-      </c>
-      <c r="I6" s="33">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="G6">
+        <v>0</v>
+      </c>
+      <c r="H6">
+        <v>0</v>
+      </c>
+      <c r="I6" s="4">
+        <v>0</v>
+      </c>
+      <c r="J6">
+        <v>0</v>
+      </c>
+      <c r="K6">
+        <v>0</v>
+      </c>
+      <c r="L6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>4</v>
       </c>
@@ -2280,26 +2732,35 @@
       <c r="C7" s="4">
         <v>1</v>
       </c>
-      <c r="D7" s="33">
-        <v>0</v>
-      </c>
-      <c r="E7" s="33">
+      <c r="D7">
+        <v>0</v>
+      </c>
+      <c r="E7">
         <v>0</v>
       </c>
       <c r="F7" s="4">
         <v>0</v>
       </c>
-      <c r="G7" s="33">
-        <v>0</v>
-      </c>
-      <c r="H7" s="33">
-        <v>0</v>
-      </c>
-      <c r="I7" s="33">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="G7">
+        <v>0</v>
+      </c>
+      <c r="H7">
+        <v>0</v>
+      </c>
+      <c r="I7" s="4">
+        <v>0</v>
+      </c>
+      <c r="J7">
+        <v>0</v>
+      </c>
+      <c r="K7">
+        <v>0</v>
+      </c>
+      <c r="L7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>5</v>
       </c>
@@ -2309,26 +2770,35 @@
       <c r="C8" s="4">
         <v>1</v>
       </c>
-      <c r="D8" s="33">
-        <v>0</v>
-      </c>
-      <c r="E8" s="33">
+      <c r="D8">
+        <v>0</v>
+      </c>
+      <c r="E8">
         <v>0</v>
       </c>
       <c r="F8" s="4">
         <v>0</v>
       </c>
-      <c r="G8" s="33">
-        <v>0</v>
-      </c>
-      <c r="H8" s="33">
-        <v>0</v>
-      </c>
-      <c r="I8" s="33">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="G8">
+        <v>0</v>
+      </c>
+      <c r="H8">
+        <v>0</v>
+      </c>
+      <c r="I8" s="4">
+        <v>0</v>
+      </c>
+      <c r="J8">
+        <v>0</v>
+      </c>
+      <c r="K8">
+        <v>0</v>
+      </c>
+      <c r="L8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>6</v>
       </c>
@@ -2338,26 +2808,35 @@
       <c r="C9" s="4">
         <v>1</v>
       </c>
-      <c r="D9" s="33">
-        <v>0</v>
-      </c>
-      <c r="E9" s="33">
+      <c r="D9">
+        <v>0</v>
+      </c>
+      <c r="E9">
         <v>0</v>
       </c>
       <c r="F9" s="4">
         <v>0</v>
       </c>
-      <c r="G9" s="33">
-        <v>0</v>
-      </c>
-      <c r="H9" s="33">
-        <v>0</v>
-      </c>
-      <c r="I9" s="33">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="G9">
+        <v>0</v>
+      </c>
+      <c r="H9">
+        <v>0</v>
+      </c>
+      <c r="I9" s="4">
+        <v>0</v>
+      </c>
+      <c r="J9">
+        <v>0</v>
+      </c>
+      <c r="K9">
+        <v>0</v>
+      </c>
+      <c r="L9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>7</v>
       </c>
@@ -2367,26 +2846,35 @@
       <c r="C10" s="4">
         <v>1</v>
       </c>
-      <c r="D10" s="33">
-        <v>0</v>
-      </c>
-      <c r="E10" s="33">
+      <c r="D10">
+        <v>0</v>
+      </c>
+      <c r="E10">
         <v>0</v>
       </c>
       <c r="F10" s="4">
         <v>0</v>
       </c>
-      <c r="G10" s="33">
-        <v>0</v>
-      </c>
-      <c r="H10" s="33">
-        <v>0</v>
-      </c>
-      <c r="I10" s="33">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="G10">
+        <v>0</v>
+      </c>
+      <c r="H10">
+        <v>0</v>
+      </c>
+      <c r="I10" s="4">
+        <v>0</v>
+      </c>
+      <c r="J10">
+        <v>0</v>
+      </c>
+      <c r="K10">
+        <v>0</v>
+      </c>
+      <c r="L10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>8</v>
       </c>
@@ -2396,26 +2884,35 @@
       <c r="C11" s="4">
         <v>1</v>
       </c>
-      <c r="D11" s="33">
-        <v>0</v>
-      </c>
-      <c r="E11" s="33">
+      <c r="D11">
+        <v>0</v>
+      </c>
+      <c r="E11">
         <v>0</v>
       </c>
       <c r="F11" s="4">
         <v>0</v>
       </c>
-      <c r="G11" s="33">
-        <v>0</v>
-      </c>
-      <c r="H11" s="33">
-        <v>0</v>
-      </c>
-      <c r="I11" s="33">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="G11">
+        <v>0</v>
+      </c>
+      <c r="H11">
+        <v>0</v>
+      </c>
+      <c r="I11" s="4">
+        <v>0</v>
+      </c>
+      <c r="J11">
+        <v>0</v>
+      </c>
+      <c r="K11">
+        <v>0</v>
+      </c>
+      <c r="L11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>9</v>
       </c>
@@ -2425,26 +2922,35 @@
       <c r="C12" s="4">
         <v>1</v>
       </c>
-      <c r="D12" s="33">
-        <v>0</v>
-      </c>
-      <c r="E12" s="33">
+      <c r="D12">
+        <v>0</v>
+      </c>
+      <c r="E12">
         <v>0</v>
       </c>
       <c r="F12" s="4">
         <v>0</v>
       </c>
-      <c r="G12" s="33">
-        <v>0</v>
-      </c>
-      <c r="H12" s="33">
-        <v>0</v>
-      </c>
-      <c r="I12" s="33">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="G12">
+        <v>0</v>
+      </c>
+      <c r="H12">
+        <v>0</v>
+      </c>
+      <c r="I12" s="4">
+        <v>0</v>
+      </c>
+      <c r="J12">
+        <v>0</v>
+      </c>
+      <c r="K12">
+        <v>0</v>
+      </c>
+      <c r="L12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>10</v>
       </c>
@@ -2454,26 +2960,35 @@
       <c r="C13" s="4">
         <v>1</v>
       </c>
-      <c r="D13" s="33">
-        <v>0</v>
-      </c>
-      <c r="E13" s="33">
+      <c r="D13">
+        <v>0</v>
+      </c>
+      <c r="E13">
         <v>0</v>
       </c>
       <c r="F13" s="4">
         <v>0</v>
       </c>
-      <c r="G13" s="33">
-        <v>0</v>
-      </c>
-      <c r="H13" s="33">
-        <v>0</v>
-      </c>
-      <c r="I13" s="33">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="G13">
+        <v>0</v>
+      </c>
+      <c r="H13">
+        <v>0</v>
+      </c>
+      <c r="I13" s="4">
+        <v>0</v>
+      </c>
+      <c r="J13">
+        <v>0</v>
+      </c>
+      <c r="K13">
+        <v>0</v>
+      </c>
+      <c r="L13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>11</v>
       </c>
@@ -2483,26 +2998,35 @@
       <c r="C14" s="4">
         <v>2</v>
       </c>
-      <c r="D14" s="33">
-        <v>0</v>
-      </c>
-      <c r="E14" s="33">
+      <c r="D14">
+        <v>0</v>
+      </c>
+      <c r="E14">
         <v>0</v>
       </c>
       <c r="F14" s="4">
         <v>0</v>
       </c>
-      <c r="G14" s="33">
-        <v>0</v>
-      </c>
-      <c r="H14" s="33">
-        <v>0</v>
-      </c>
-      <c r="I14" s="33">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="G14">
+        <v>0</v>
+      </c>
+      <c r="H14">
+        <v>0</v>
+      </c>
+      <c r="I14" s="4">
+        <v>0</v>
+      </c>
+      <c r="J14">
+        <v>0</v>
+      </c>
+      <c r="K14">
+        <v>0</v>
+      </c>
+      <c r="L14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A15">
         <v>12</v>
       </c>
@@ -2512,26 +3036,35 @@
       <c r="C15" s="4">
         <v>2</v>
       </c>
-      <c r="D15" s="33">
-        <v>0</v>
-      </c>
-      <c r="E15" s="33">
+      <c r="D15">
+        <v>0</v>
+      </c>
+      <c r="E15">
         <v>0</v>
       </c>
       <c r="F15" s="4">
         <v>0</v>
       </c>
-      <c r="G15" s="33">
-        <v>0</v>
-      </c>
-      <c r="H15" s="33">
-        <v>0</v>
-      </c>
-      <c r="I15" s="33">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="G15">
+        <v>0</v>
+      </c>
+      <c r="H15">
+        <v>0</v>
+      </c>
+      <c r="I15" s="4">
+        <v>0</v>
+      </c>
+      <c r="J15">
+        <v>0</v>
+      </c>
+      <c r="K15">
+        <v>0</v>
+      </c>
+      <c r="L15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A16">
         <v>13</v>
       </c>
@@ -2541,26 +3074,35 @@
       <c r="C16" s="4">
         <v>2</v>
       </c>
-      <c r="D16" s="33">
-        <v>0</v>
-      </c>
-      <c r="E16" s="33">
+      <c r="D16">
+        <v>0</v>
+      </c>
+      <c r="E16">
         <v>0</v>
       </c>
       <c r="F16" s="4">
         <v>0</v>
       </c>
-      <c r="G16" s="33">
-        <v>0</v>
-      </c>
-      <c r="H16" s="33">
-        <v>0</v>
-      </c>
-      <c r="I16" s="33">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="G16">
+        <v>0</v>
+      </c>
+      <c r="H16">
+        <v>0</v>
+      </c>
+      <c r="I16" s="4">
+        <v>0</v>
+      </c>
+      <c r="J16">
+        <v>0</v>
+      </c>
+      <c r="K16">
+        <v>0</v>
+      </c>
+      <c r="L16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A17">
         <v>14</v>
       </c>
@@ -2570,26 +3112,35 @@
       <c r="C17" s="4">
         <v>2</v>
       </c>
-      <c r="D17" s="33">
-        <v>0</v>
-      </c>
-      <c r="E17" s="33">
+      <c r="D17">
+        <v>0</v>
+      </c>
+      <c r="E17">
         <v>0</v>
       </c>
       <c r="F17" s="4">
         <v>0</v>
       </c>
-      <c r="G17" s="33">
-        <v>0</v>
-      </c>
-      <c r="H17" s="33">
-        <v>0</v>
-      </c>
-      <c r="I17" s="33">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="G17">
+        <v>0</v>
+      </c>
+      <c r="H17">
+        <v>0</v>
+      </c>
+      <c r="I17" s="4">
+        <v>0</v>
+      </c>
+      <c r="J17">
+        <v>0</v>
+      </c>
+      <c r="K17">
+        <v>0</v>
+      </c>
+      <c r="L17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A18">
         <v>15</v>
       </c>
@@ -2599,26 +3150,35 @@
       <c r="C18" s="4">
         <v>2</v>
       </c>
-      <c r="D18" s="33">
-        <v>0</v>
-      </c>
-      <c r="E18" s="33">
+      <c r="D18">
+        <v>0</v>
+      </c>
+      <c r="E18">
         <v>0</v>
       </c>
       <c r="F18" s="4">
         <v>0</v>
       </c>
-      <c r="G18" s="33">
-        <v>0</v>
-      </c>
-      <c r="H18" s="33">
-        <v>0</v>
-      </c>
-      <c r="I18" s="33">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="G18">
+        <v>0</v>
+      </c>
+      <c r="H18">
+        <v>0</v>
+      </c>
+      <c r="I18" s="4">
+        <v>0</v>
+      </c>
+      <c r="J18">
+        <v>0</v>
+      </c>
+      <c r="K18">
+        <v>0</v>
+      </c>
+      <c r="L18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A19">
         <v>16</v>
       </c>
@@ -2628,26 +3188,35 @@
       <c r="C19" s="4">
         <v>2</v>
       </c>
-      <c r="D19" s="33">
-        <v>0</v>
-      </c>
-      <c r="E19" s="33">
+      <c r="D19">
+        <v>0</v>
+      </c>
+      <c r="E19">
         <v>0</v>
       </c>
       <c r="F19" s="4">
         <v>0</v>
       </c>
-      <c r="G19" s="33">
-        <v>0</v>
-      </c>
-      <c r="H19" s="33">
-        <v>0</v>
-      </c>
-      <c r="I19" s="33">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="G19">
+        <v>0</v>
+      </c>
+      <c r="H19">
+        <v>0</v>
+      </c>
+      <c r="I19" s="4">
+        <v>0</v>
+      </c>
+      <c r="J19">
+        <v>0</v>
+      </c>
+      <c r="K19">
+        <v>0</v>
+      </c>
+      <c r="L19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A20">
         <v>17</v>
       </c>
@@ -2657,26 +3226,35 @@
       <c r="C20" s="4">
         <v>2</v>
       </c>
-      <c r="D20" s="33">
-        <v>0</v>
-      </c>
-      <c r="E20" s="33">
+      <c r="D20">
+        <v>0</v>
+      </c>
+      <c r="E20">
         <v>0</v>
       </c>
       <c r="F20" s="4">
         <v>0</v>
       </c>
-      <c r="G20" s="33">
-        <v>0</v>
-      </c>
-      <c r="H20" s="33">
-        <v>0</v>
-      </c>
-      <c r="I20" s="33">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="G20">
+        <v>0</v>
+      </c>
+      <c r="H20">
+        <v>0</v>
+      </c>
+      <c r="I20" s="4">
+        <v>0</v>
+      </c>
+      <c r="J20">
+        <v>0</v>
+      </c>
+      <c r="K20">
+        <v>0</v>
+      </c>
+      <c r="L20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A21">
         <v>18</v>
       </c>
@@ -2686,26 +3264,35 @@
       <c r="C21" s="4">
         <v>2</v>
       </c>
-      <c r="D21" s="33">
-        <v>0</v>
-      </c>
-      <c r="E21" s="33">
+      <c r="D21">
+        <v>0</v>
+      </c>
+      <c r="E21">
         <v>0</v>
       </c>
       <c r="F21" s="4">
         <v>0</v>
       </c>
-      <c r="G21" s="33">
-        <v>0</v>
-      </c>
-      <c r="H21" s="33">
-        <v>0</v>
-      </c>
-      <c r="I21" s="33">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="G21">
+        <v>0</v>
+      </c>
+      <c r="H21">
+        <v>0</v>
+      </c>
+      <c r="I21" s="4">
+        <v>0</v>
+      </c>
+      <c r="J21">
+        <v>0</v>
+      </c>
+      <c r="K21">
+        <v>0</v>
+      </c>
+      <c r="L21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A22">
         <v>19</v>
       </c>
@@ -2715,26 +3302,35 @@
       <c r="C22" s="4">
         <v>2</v>
       </c>
-      <c r="D22" s="33">
-        <v>0</v>
-      </c>
-      <c r="E22" s="33">
+      <c r="D22">
+        <v>0</v>
+      </c>
+      <c r="E22">
         <v>0</v>
       </c>
       <c r="F22" s="4">
         <v>0</v>
       </c>
-      <c r="G22" s="33">
-        <v>0</v>
-      </c>
-      <c r="H22" s="33">
-        <v>0</v>
-      </c>
-      <c r="I22" s="33">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="G22">
+        <v>0</v>
+      </c>
+      <c r="H22">
+        <v>0</v>
+      </c>
+      <c r="I22" s="4">
+        <v>0</v>
+      </c>
+      <c r="J22">
+        <v>0</v>
+      </c>
+      <c r="K22">
+        <v>0</v>
+      </c>
+      <c r="L22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A23">
         <v>20</v>
       </c>
@@ -2744,26 +3340,35 @@
       <c r="C23" s="4">
         <v>2</v>
       </c>
-      <c r="D23" s="33">
-        <v>0</v>
-      </c>
-      <c r="E23" s="33">
+      <c r="D23">
+        <v>0</v>
+      </c>
+      <c r="E23">
         <v>0</v>
       </c>
       <c r="F23" s="4">
         <v>0</v>
       </c>
-      <c r="G23" s="33">
-        <v>0</v>
-      </c>
-      <c r="H23" s="33">
-        <v>0</v>
-      </c>
-      <c r="I23" s="33">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="G23">
+        <v>0</v>
+      </c>
+      <c r="H23">
+        <v>0</v>
+      </c>
+      <c r="I23" s="4">
+        <v>0</v>
+      </c>
+      <c r="J23">
+        <v>0</v>
+      </c>
+      <c r="K23">
+        <v>0</v>
+      </c>
+      <c r="L23">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A24">
         <v>21</v>
       </c>
@@ -2773,26 +3378,35 @@
       <c r="C24" s="4">
         <v>2</v>
       </c>
-      <c r="D24" s="33">
-        <v>0</v>
-      </c>
-      <c r="E24" s="33">
+      <c r="D24">
+        <v>0</v>
+      </c>
+      <c r="E24">
         <v>0</v>
       </c>
       <c r="F24" s="4">
         <v>0</v>
       </c>
-      <c r="G24" s="33">
-        <v>0</v>
-      </c>
-      <c r="H24" s="33">
-        <v>0</v>
-      </c>
-      <c r="I24" s="33">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="G24">
+        <v>0</v>
+      </c>
+      <c r="H24">
+        <v>0</v>
+      </c>
+      <c r="I24" s="4">
+        <v>0</v>
+      </c>
+      <c r="J24">
+        <v>0</v>
+      </c>
+      <c r="K24">
+        <v>0</v>
+      </c>
+      <c r="L24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A25">
         <v>22</v>
       </c>
@@ -2802,26 +3416,35 @@
       <c r="C25" s="4">
         <v>3</v>
       </c>
-      <c r="D25" s="33">
-        <v>0</v>
-      </c>
-      <c r="E25" s="33">
+      <c r="D25">
+        <v>0</v>
+      </c>
+      <c r="E25">
         <v>0</v>
       </c>
       <c r="F25" s="4">
         <v>0</v>
       </c>
-      <c r="G25" s="33">
-        <v>0</v>
-      </c>
-      <c r="H25" s="33">
-        <v>0</v>
-      </c>
-      <c r="I25" s="33">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="G25">
+        <v>0</v>
+      </c>
+      <c r="H25">
+        <v>0</v>
+      </c>
+      <c r="I25" s="4">
+        <v>0</v>
+      </c>
+      <c r="J25">
+        <v>0</v>
+      </c>
+      <c r="K25">
+        <v>0</v>
+      </c>
+      <c r="L25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A26">
         <v>23</v>
       </c>
@@ -2831,26 +3454,35 @@
       <c r="C26" s="4">
         <v>3</v>
       </c>
-      <c r="D26" s="33">
-        <v>0</v>
-      </c>
-      <c r="E26" s="33">
+      <c r="D26">
+        <v>0</v>
+      </c>
+      <c r="E26">
         <v>0</v>
       </c>
       <c r="F26" s="4">
         <v>0</v>
       </c>
-      <c r="G26" s="33">
-        <v>0</v>
-      </c>
-      <c r="H26" s="33">
-        <v>0</v>
-      </c>
-      <c r="I26" s="33">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="G26">
+        <v>0</v>
+      </c>
+      <c r="H26">
+        <v>0</v>
+      </c>
+      <c r="I26" s="4">
+        <v>0</v>
+      </c>
+      <c r="J26">
+        <v>0</v>
+      </c>
+      <c r="K26">
+        <v>0</v>
+      </c>
+      <c r="L26">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A27">
         <v>24</v>
       </c>
@@ -2860,26 +3492,35 @@
       <c r="C27" s="4">
         <v>3</v>
       </c>
-      <c r="D27" s="33">
-        <v>0</v>
-      </c>
-      <c r="E27" s="33">
+      <c r="D27">
+        <v>0</v>
+      </c>
+      <c r="E27">
         <v>0</v>
       </c>
       <c r="F27" s="4">
         <v>0</v>
       </c>
-      <c r="G27" s="33">
-        <v>0</v>
-      </c>
-      <c r="H27" s="33">
-        <v>0</v>
-      </c>
-      <c r="I27" s="33">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="G27">
+        <v>0</v>
+      </c>
+      <c r="H27">
+        <v>0</v>
+      </c>
+      <c r="I27" s="4">
+        <v>0</v>
+      </c>
+      <c r="J27">
+        <v>0</v>
+      </c>
+      <c r="K27">
+        <v>0</v>
+      </c>
+      <c r="L27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A28">
         <v>25</v>
       </c>
@@ -2889,26 +3530,35 @@
       <c r="C28" s="4">
         <v>3</v>
       </c>
-      <c r="D28" s="33">
-        <v>0</v>
-      </c>
-      <c r="E28" s="33">
+      <c r="D28">
+        <v>0</v>
+      </c>
+      <c r="E28">
         <v>0</v>
       </c>
       <c r="F28" s="4">
         <v>0</v>
       </c>
-      <c r="G28" s="33">
-        <v>0</v>
-      </c>
-      <c r="H28" s="33">
-        <v>0</v>
-      </c>
-      <c r="I28" s="33">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="G28">
+        <v>0</v>
+      </c>
+      <c r="H28">
+        <v>0</v>
+      </c>
+      <c r="I28" s="4">
+        <v>0</v>
+      </c>
+      <c r="J28">
+        <v>0</v>
+      </c>
+      <c r="K28">
+        <v>0</v>
+      </c>
+      <c r="L28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A29">
         <v>26</v>
       </c>
@@ -2918,26 +3568,35 @@
       <c r="C29" s="4">
         <v>3</v>
       </c>
-      <c r="D29" s="33">
-        <v>0</v>
-      </c>
-      <c r="E29" s="33">
+      <c r="D29">
+        <v>0</v>
+      </c>
+      <c r="E29">
         <v>0</v>
       </c>
       <c r="F29" s="4">
         <v>0</v>
       </c>
-      <c r="G29" s="33">
-        <v>0</v>
-      </c>
-      <c r="H29" s="33">
-        <v>0</v>
-      </c>
-      <c r="I29" s="33">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="G29">
+        <v>0</v>
+      </c>
+      <c r="H29">
+        <v>0</v>
+      </c>
+      <c r="I29" s="4">
+        <v>0</v>
+      </c>
+      <c r="J29">
+        <v>0</v>
+      </c>
+      <c r="K29">
+        <v>0</v>
+      </c>
+      <c r="L29">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A30">
         <v>27</v>
       </c>
@@ -2947,26 +3606,35 @@
       <c r="C30" s="4">
         <v>3</v>
       </c>
-      <c r="D30" s="33">
-        <v>0</v>
-      </c>
-      <c r="E30" s="33">
+      <c r="D30">
+        <v>0</v>
+      </c>
+      <c r="E30">
         <v>0</v>
       </c>
       <c r="F30" s="4">
         <v>0</v>
       </c>
-      <c r="G30" s="33">
-        <v>0</v>
-      </c>
-      <c r="H30" s="33">
-        <v>0</v>
-      </c>
-      <c r="I30" s="33">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="31" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="G30">
+        <v>0</v>
+      </c>
+      <c r="H30">
+        <v>0</v>
+      </c>
+      <c r="I30" s="4">
+        <v>0</v>
+      </c>
+      <c r="J30">
+        <v>0</v>
+      </c>
+      <c r="K30">
+        <v>0</v>
+      </c>
+      <c r="L30">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A31">
         <v>28</v>
       </c>
@@ -2976,26 +3644,35 @@
       <c r="C31" s="4">
         <v>3</v>
       </c>
-      <c r="D31" s="33">
-        <v>0</v>
-      </c>
-      <c r="E31" s="33">
+      <c r="D31">
+        <v>0</v>
+      </c>
+      <c r="E31">
         <v>0</v>
       </c>
       <c r="F31" s="4">
         <v>0</v>
       </c>
-      <c r="G31" s="33">
-        <v>0</v>
-      </c>
-      <c r="H31" s="33">
-        <v>0</v>
-      </c>
-      <c r="I31" s="33">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="32" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="G31">
+        <v>0</v>
+      </c>
+      <c r="H31">
+        <v>0</v>
+      </c>
+      <c r="I31" s="4">
+        <v>0</v>
+      </c>
+      <c r="J31">
+        <v>0</v>
+      </c>
+      <c r="K31">
+        <v>0</v>
+      </c>
+      <c r="L31">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A32">
         <v>29</v>
       </c>
@@ -3005,26 +3682,35 @@
       <c r="C32" s="4">
         <v>3</v>
       </c>
-      <c r="D32" s="33">
-        <v>0</v>
-      </c>
-      <c r="E32" s="33">
+      <c r="D32">
+        <v>0</v>
+      </c>
+      <c r="E32">
         <v>0</v>
       </c>
       <c r="F32" s="4">
         <v>0</v>
       </c>
-      <c r="G32" s="33">
-        <v>0</v>
-      </c>
-      <c r="H32" s="33">
-        <v>0</v>
-      </c>
-      <c r="I32" s="33">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="33" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="G32">
+        <v>0</v>
+      </c>
+      <c r="H32">
+        <v>0</v>
+      </c>
+      <c r="I32" s="4">
+        <v>0</v>
+      </c>
+      <c r="J32">
+        <v>0</v>
+      </c>
+      <c r="K32">
+        <v>0</v>
+      </c>
+      <c r="L32">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A33">
         <v>30</v>
       </c>
@@ -3034,26 +3720,35 @@
       <c r="C33" s="4">
         <v>3</v>
       </c>
-      <c r="D33" s="33">
-        <v>0</v>
-      </c>
-      <c r="E33" s="33">
+      <c r="D33">
+        <v>0</v>
+      </c>
+      <c r="E33">
         <v>0</v>
       </c>
       <c r="F33" s="4">
         <v>0</v>
       </c>
-      <c r="G33" s="33">
-        <v>0</v>
-      </c>
-      <c r="H33" s="33">
-        <v>0</v>
-      </c>
-      <c r="I33" s="33">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="34" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="G33">
+        <v>0</v>
+      </c>
+      <c r="H33">
+        <v>0</v>
+      </c>
+      <c r="I33" s="4">
+        <v>0</v>
+      </c>
+      <c r="J33">
+        <v>0</v>
+      </c>
+      <c r="K33">
+        <v>0</v>
+      </c>
+      <c r="L33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A34">
         <v>31</v>
       </c>
@@ -3063,26 +3758,35 @@
       <c r="C34" s="4">
         <v>3</v>
       </c>
-      <c r="D34" s="33">
-        <v>0</v>
-      </c>
-      <c r="E34" s="33">
+      <c r="D34">
+        <v>0</v>
+      </c>
+      <c r="E34">
         <v>0</v>
       </c>
       <c r="F34" s="4">
         <v>0</v>
       </c>
-      <c r="G34" s="33">
-        <v>0</v>
-      </c>
-      <c r="H34" s="33">
-        <v>0</v>
-      </c>
-      <c r="I34" s="33">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="35" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="G34">
+        <v>0</v>
+      </c>
+      <c r="H34">
+        <v>0</v>
+      </c>
+      <c r="I34" s="4">
+        <v>0</v>
+      </c>
+      <c r="J34">
+        <v>0</v>
+      </c>
+      <c r="K34">
+        <v>0</v>
+      </c>
+      <c r="L34">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A35">
         <v>32</v>
       </c>
@@ -3092,22 +3796,31 @@
       <c r="C35" s="4">
         <v>3</v>
       </c>
-      <c r="D35" s="33">
-        <v>0</v>
-      </c>
-      <c r="E35" s="33">
+      <c r="D35">
+        <v>0</v>
+      </c>
+      <c r="E35">
         <v>0</v>
       </c>
       <c r="F35" s="4">
         <v>0</v>
       </c>
-      <c r="G35" s="33">
-        <v>0</v>
-      </c>
-      <c r="H35" s="33">
-        <v>0</v>
-      </c>
-      <c r="I35" s="33">
+      <c r="G35">
+        <v>0</v>
+      </c>
+      <c r="H35">
+        <v>0</v>
+      </c>
+      <c r="I35" s="4">
+        <v>0</v>
+      </c>
+      <c r="J35">
+        <v>0</v>
+      </c>
+      <c r="K35">
+        <v>0</v>
+      </c>
+      <c r="L35">
         <v>0</v>
       </c>
     </row>
@@ -3119,68 +3832,86 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6106EBB4-9662-4573-BA72-1B567CFB0AC4}">
-  <dimension ref="A1:I35"/>
+  <dimension ref="A1:L35"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A1" s="25" t="s">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A1" s="21" t="s">
         <v>12</v>
       </c>
-      <c r="B1" s="25" t="s">
+      <c r="B1" s="21" t="s">
         <v>31</v>
       </c>
-      <c r="C1" s="27" t="s">
+      <c r="C1" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="D1" s="29" t="s">
+      <c r="D1" s="25" t="s">
         <v>32</v>
       </c>
-      <c r="E1" s="29" t="s">
+      <c r="E1" s="25" t="s">
         <v>33</v>
       </c>
-      <c r="F1" s="30" t="s">
+      <c r="F1" s="26" t="s">
         <v>34</v>
       </c>
-      <c r="G1" s="29" t="s">
+      <c r="G1" s="25" t="s">
+        <v>41</v>
+      </c>
+      <c r="H1" s="25" t="s">
         <v>42</v>
       </c>
-      <c r="H1" s="29" t="s">
+      <c r="I1" s="26" t="s">
         <v>43</v>
       </c>
-      <c r="I1" s="29" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="2" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="26" t="s">
+      <c r="J1" s="25" t="s">
+        <v>48</v>
+      </c>
+      <c r="K1" s="25" t="s">
+        <v>49</v>
+      </c>
+      <c r="L1" s="25" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="22" t="s">
         <v>14</v>
       </c>
-      <c r="B2" s="26" t="s">
+      <c r="B2" s="22" t="s">
         <v>14</v>
       </c>
-      <c r="C2" s="28" t="s">
+      <c r="C2" s="24" t="s">
         <v>15</v>
       </c>
-      <c r="D2" s="31" t="s">
-        <v>48</v>
-      </c>
-      <c r="E2" s="31" t="s">
-        <v>48</v>
-      </c>
-      <c r="F2" s="32" t="s">
-        <v>48</v>
-      </c>
-      <c r="G2" s="31" t="s">
-        <v>49</v>
-      </c>
-      <c r="H2" s="31" t="s">
-        <v>49</v>
-      </c>
-      <c r="I2" s="31" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="3" spans="1:9" ht="15" thickTop="1" x14ac:dyDescent="0.3">
+      <c r="D2" s="27" t="s">
+        <v>46</v>
+      </c>
+      <c r="E2" s="27" t="s">
+        <v>46</v>
+      </c>
+      <c r="F2" s="28" t="s">
+        <v>46</v>
+      </c>
+      <c r="G2" s="27" t="s">
+        <v>47</v>
+      </c>
+      <c r="H2" s="27" t="s">
+        <v>47</v>
+      </c>
+      <c r="I2" s="28" t="s">
+        <v>47</v>
+      </c>
+      <c r="J2" s="27" t="s">
+        <v>47</v>
+      </c>
+      <c r="K2" s="27" t="s">
+        <v>47</v>
+      </c>
+      <c r="L2" s="27" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" ht="15" thickTop="1" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>0</v>
       </c>
@@ -3190,26 +3921,35 @@
       <c r="C3" s="4">
         <v>1</v>
       </c>
-      <c r="D3" s="33">
-        <v>0</v>
-      </c>
-      <c r="E3" s="33">
+      <c r="D3">
+        <v>0</v>
+      </c>
+      <c r="E3">
         <v>0</v>
       </c>
       <c r="F3" s="4">
         <v>0</v>
       </c>
-      <c r="G3" s="33">
-        <v>0</v>
-      </c>
-      <c r="H3" s="33">
-        <v>0</v>
-      </c>
-      <c r="I3" s="33">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="G3">
+        <v>0</v>
+      </c>
+      <c r="H3">
+        <v>0</v>
+      </c>
+      <c r="I3" s="4">
+        <v>0</v>
+      </c>
+      <c r="J3">
+        <v>0</v>
+      </c>
+      <c r="K3">
+        <v>0</v>
+      </c>
+      <c r="L3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>1</v>
       </c>
@@ -3219,26 +3959,35 @@
       <c r="C4" s="4">
         <v>1</v>
       </c>
-      <c r="D4" s="33">
-        <v>0</v>
-      </c>
-      <c r="E4" s="33">
+      <c r="D4">
+        <v>0</v>
+      </c>
+      <c r="E4">
         <v>0</v>
       </c>
       <c r="F4" s="4">
         <v>0</v>
       </c>
-      <c r="G4" s="33">
-        <v>0</v>
-      </c>
-      <c r="H4" s="33">
-        <v>0</v>
-      </c>
-      <c r="I4" s="33">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="G4">
+        <v>0</v>
+      </c>
+      <c r="H4">
+        <v>0</v>
+      </c>
+      <c r="I4" s="4">
+        <v>0</v>
+      </c>
+      <c r="J4">
+        <v>0</v>
+      </c>
+      <c r="K4">
+        <v>0</v>
+      </c>
+      <c r="L4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>2</v>
       </c>
@@ -3248,26 +3997,35 @@
       <c r="C5" s="4">
         <v>1</v>
       </c>
-      <c r="D5" s="33">
-        <v>0</v>
-      </c>
-      <c r="E5" s="33">
+      <c r="D5">
+        <v>0</v>
+      </c>
+      <c r="E5">
         <v>0</v>
       </c>
       <c r="F5" s="4">
         <v>0</v>
       </c>
-      <c r="G5" s="33">
-        <v>0</v>
-      </c>
-      <c r="H5" s="33">
-        <v>0</v>
-      </c>
-      <c r="I5" s="33">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="G5">
+        <v>0</v>
+      </c>
+      <c r="H5">
+        <v>0</v>
+      </c>
+      <c r="I5" s="4">
+        <v>0</v>
+      </c>
+      <c r="J5">
+        <v>0</v>
+      </c>
+      <c r="K5">
+        <v>0</v>
+      </c>
+      <c r="L5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>3</v>
       </c>
@@ -3277,26 +4035,35 @@
       <c r="C6" s="4">
         <v>1</v>
       </c>
-      <c r="D6" s="33">
-        <v>0</v>
-      </c>
-      <c r="E6" s="33">
+      <c r="D6">
+        <v>0</v>
+      </c>
+      <c r="E6">
         <v>0</v>
       </c>
       <c r="F6" s="4">
         <v>0</v>
       </c>
-      <c r="G6" s="33">
-        <v>0</v>
-      </c>
-      <c r="H6" s="33">
-        <v>0</v>
-      </c>
-      <c r="I6" s="33">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="G6">
+        <v>0</v>
+      </c>
+      <c r="H6">
+        <v>0</v>
+      </c>
+      <c r="I6" s="4">
+        <v>0</v>
+      </c>
+      <c r="J6">
+        <v>0</v>
+      </c>
+      <c r="K6">
+        <v>0</v>
+      </c>
+      <c r="L6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>4</v>
       </c>
@@ -3306,26 +4073,35 @@
       <c r="C7" s="4">
         <v>1</v>
       </c>
-      <c r="D7" s="33">
-        <v>0</v>
-      </c>
-      <c r="E7" s="33">
+      <c r="D7">
+        <v>0</v>
+      </c>
+      <c r="E7">
         <v>0</v>
       </c>
       <c r="F7" s="4">
         <v>0</v>
       </c>
-      <c r="G7" s="33">
-        <v>0</v>
-      </c>
-      <c r="H7" s="33">
-        <v>0</v>
-      </c>
-      <c r="I7" s="33">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="G7">
+        <v>0</v>
+      </c>
+      <c r="H7">
+        <v>0</v>
+      </c>
+      <c r="I7" s="4">
+        <v>0</v>
+      </c>
+      <c r="J7">
+        <v>0</v>
+      </c>
+      <c r="K7">
+        <v>0</v>
+      </c>
+      <c r="L7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>5</v>
       </c>
@@ -3335,26 +4111,35 @@
       <c r="C8" s="4">
         <v>1</v>
       </c>
-      <c r="D8" s="33">
-        <v>0</v>
-      </c>
-      <c r="E8" s="33">
+      <c r="D8">
+        <v>0</v>
+      </c>
+      <c r="E8">
         <v>0</v>
       </c>
       <c r="F8" s="4">
         <v>0</v>
       </c>
-      <c r="G8" s="33">
-        <v>0</v>
-      </c>
-      <c r="H8" s="33">
-        <v>0</v>
-      </c>
-      <c r="I8" s="33">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="G8">
+        <v>0</v>
+      </c>
+      <c r="H8">
+        <v>0</v>
+      </c>
+      <c r="I8" s="4">
+        <v>0</v>
+      </c>
+      <c r="J8">
+        <v>0</v>
+      </c>
+      <c r="K8">
+        <v>0</v>
+      </c>
+      <c r="L8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>6</v>
       </c>
@@ -3364,26 +4149,35 @@
       <c r="C9" s="4">
         <v>1</v>
       </c>
-      <c r="D9" s="33">
-        <v>0</v>
-      </c>
-      <c r="E9" s="33">
+      <c r="D9">
+        <v>0</v>
+      </c>
+      <c r="E9">
         <v>0</v>
       </c>
       <c r="F9" s="4">
         <v>0</v>
       </c>
-      <c r="G9" s="33">
-        <v>0</v>
-      </c>
-      <c r="H9" s="33">
-        <v>0</v>
-      </c>
-      <c r="I9" s="33">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="G9">
+        <v>0</v>
+      </c>
+      <c r="H9">
+        <v>0</v>
+      </c>
+      <c r="I9" s="4">
+        <v>0</v>
+      </c>
+      <c r="J9">
+        <v>0</v>
+      </c>
+      <c r="K9">
+        <v>0</v>
+      </c>
+      <c r="L9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>7</v>
       </c>
@@ -3393,26 +4187,35 @@
       <c r="C10" s="4">
         <v>1</v>
       </c>
-      <c r="D10" s="33">
-        <v>0</v>
-      </c>
-      <c r="E10" s="33">
+      <c r="D10">
+        <v>0</v>
+      </c>
+      <c r="E10">
         <v>0</v>
       </c>
       <c r="F10" s="4">
         <v>0</v>
       </c>
-      <c r="G10" s="33">
-        <v>0</v>
-      </c>
-      <c r="H10" s="33">
-        <v>0</v>
-      </c>
-      <c r="I10" s="33">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="G10">
+        <v>0</v>
+      </c>
+      <c r="H10">
+        <v>0</v>
+      </c>
+      <c r="I10" s="4">
+        <v>0</v>
+      </c>
+      <c r="J10">
+        <v>0</v>
+      </c>
+      <c r="K10">
+        <v>0</v>
+      </c>
+      <c r="L10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>8</v>
       </c>
@@ -3422,26 +4225,35 @@
       <c r="C11" s="4">
         <v>1</v>
       </c>
-      <c r="D11" s="33">
-        <v>0</v>
-      </c>
-      <c r="E11" s="33">
+      <c r="D11">
+        <v>0</v>
+      </c>
+      <c r="E11">
         <v>0</v>
       </c>
       <c r="F11" s="4">
         <v>0</v>
       </c>
-      <c r="G11" s="33">
-        <v>0</v>
-      </c>
-      <c r="H11" s="33">
-        <v>0</v>
-      </c>
-      <c r="I11" s="33">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="G11">
+        <v>0</v>
+      </c>
+      <c r="H11">
+        <v>0</v>
+      </c>
+      <c r="I11" s="4">
+        <v>0</v>
+      </c>
+      <c r="J11">
+        <v>0</v>
+      </c>
+      <c r="K11">
+        <v>0</v>
+      </c>
+      <c r="L11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>9</v>
       </c>
@@ -3451,26 +4263,35 @@
       <c r="C12" s="4">
         <v>1</v>
       </c>
-      <c r="D12" s="33">
-        <v>0</v>
-      </c>
-      <c r="E12" s="33">
+      <c r="D12">
+        <v>0</v>
+      </c>
+      <c r="E12">
         <v>0</v>
       </c>
       <c r="F12" s="4">
         <v>0</v>
       </c>
-      <c r="G12" s="33">
-        <v>0</v>
-      </c>
-      <c r="H12" s="33">
-        <v>0</v>
-      </c>
-      <c r="I12" s="33">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="G12">
+        <v>0</v>
+      </c>
+      <c r="H12">
+        <v>0</v>
+      </c>
+      <c r="I12" s="4">
+        <v>0</v>
+      </c>
+      <c r="J12">
+        <v>0</v>
+      </c>
+      <c r="K12">
+        <v>0</v>
+      </c>
+      <c r="L12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>10</v>
       </c>
@@ -3480,26 +4301,35 @@
       <c r="C13" s="4">
         <v>1</v>
       </c>
-      <c r="D13" s="33">
-        <v>0</v>
-      </c>
-      <c r="E13" s="33">
+      <c r="D13">
+        <v>0</v>
+      </c>
+      <c r="E13">
         <v>0</v>
       </c>
       <c r="F13" s="4">
         <v>0</v>
       </c>
-      <c r="G13" s="33">
-        <v>0</v>
-      </c>
-      <c r="H13" s="33">
-        <v>0</v>
-      </c>
-      <c r="I13" s="33">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="G13">
+        <v>0</v>
+      </c>
+      <c r="H13">
+        <v>0</v>
+      </c>
+      <c r="I13" s="4">
+        <v>0</v>
+      </c>
+      <c r="J13">
+        <v>0</v>
+      </c>
+      <c r="K13">
+        <v>0</v>
+      </c>
+      <c r="L13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>11</v>
       </c>
@@ -3509,26 +4339,35 @@
       <c r="C14" s="4">
         <v>2</v>
       </c>
-      <c r="D14" s="33">
-        <v>0</v>
-      </c>
-      <c r="E14" s="33">
+      <c r="D14">
+        <v>0</v>
+      </c>
+      <c r="E14">
         <v>0</v>
       </c>
       <c r="F14" s="4">
         <v>0</v>
       </c>
-      <c r="G14" s="33">
-        <v>0</v>
-      </c>
-      <c r="H14" s="33">
-        <v>0</v>
-      </c>
-      <c r="I14" s="33">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="G14">
+        <v>0</v>
+      </c>
+      <c r="H14">
+        <v>0</v>
+      </c>
+      <c r="I14" s="4">
+        <v>0</v>
+      </c>
+      <c r="J14">
+        <v>0</v>
+      </c>
+      <c r="K14">
+        <v>0</v>
+      </c>
+      <c r="L14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A15">
         <v>12</v>
       </c>
@@ -3538,26 +4377,35 @@
       <c r="C15" s="4">
         <v>2</v>
       </c>
-      <c r="D15" s="33">
-        <v>0</v>
-      </c>
-      <c r="E15" s="33">
+      <c r="D15">
+        <v>0</v>
+      </c>
+      <c r="E15">
         <v>0</v>
       </c>
       <c r="F15" s="4">
         <v>0</v>
       </c>
-      <c r="G15" s="33">
-        <v>0</v>
-      </c>
-      <c r="H15" s="33">
-        <v>0</v>
-      </c>
-      <c r="I15" s="33">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="G15">
+        <v>0</v>
+      </c>
+      <c r="H15">
+        <v>0</v>
+      </c>
+      <c r="I15" s="4">
+        <v>0</v>
+      </c>
+      <c r="J15">
+        <v>0</v>
+      </c>
+      <c r="K15">
+        <v>0</v>
+      </c>
+      <c r="L15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A16">
         <v>13</v>
       </c>
@@ -3567,26 +4415,35 @@
       <c r="C16" s="4">
         <v>2</v>
       </c>
-      <c r="D16" s="33">
-        <v>0</v>
-      </c>
-      <c r="E16" s="33">
+      <c r="D16">
+        <v>0</v>
+      </c>
+      <c r="E16">
         <v>0</v>
       </c>
       <c r="F16" s="4">
         <v>0</v>
       </c>
-      <c r="G16" s="33">
-        <v>0</v>
-      </c>
-      <c r="H16" s="33">
-        <v>0</v>
-      </c>
-      <c r="I16" s="33">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="G16">
+        <v>0</v>
+      </c>
+      <c r="H16">
+        <v>0</v>
+      </c>
+      <c r="I16" s="4">
+        <v>0</v>
+      </c>
+      <c r="J16">
+        <v>0</v>
+      </c>
+      <c r="K16">
+        <v>0</v>
+      </c>
+      <c r="L16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A17">
         <v>14</v>
       </c>
@@ -3596,26 +4453,35 @@
       <c r="C17" s="4">
         <v>2</v>
       </c>
-      <c r="D17" s="33">
-        <v>0</v>
-      </c>
-      <c r="E17" s="33">
+      <c r="D17">
+        <v>0</v>
+      </c>
+      <c r="E17">
         <v>0</v>
       </c>
       <c r="F17" s="4">
         <v>0</v>
       </c>
-      <c r="G17" s="33">
-        <v>0</v>
-      </c>
-      <c r="H17" s="33">
-        <v>0</v>
-      </c>
-      <c r="I17" s="33">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="G17">
+        <v>0</v>
+      </c>
+      <c r="H17">
+        <v>0</v>
+      </c>
+      <c r="I17" s="4">
+        <v>0</v>
+      </c>
+      <c r="J17">
+        <v>0</v>
+      </c>
+      <c r="K17">
+        <v>0</v>
+      </c>
+      <c r="L17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A18">
         <v>15</v>
       </c>
@@ -3625,26 +4491,35 @@
       <c r="C18" s="4">
         <v>2</v>
       </c>
-      <c r="D18" s="33">
-        <v>0</v>
-      </c>
-      <c r="E18" s="33">
+      <c r="D18">
+        <v>0</v>
+      </c>
+      <c r="E18">
         <v>0</v>
       </c>
       <c r="F18" s="4">
         <v>0</v>
       </c>
-      <c r="G18" s="33">
-        <v>0</v>
-      </c>
-      <c r="H18" s="33">
-        <v>0</v>
-      </c>
-      <c r="I18" s="33">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="G18">
+        <v>0</v>
+      </c>
+      <c r="H18">
+        <v>0</v>
+      </c>
+      <c r="I18" s="4">
+        <v>0</v>
+      </c>
+      <c r="J18">
+        <v>0</v>
+      </c>
+      <c r="K18">
+        <v>0</v>
+      </c>
+      <c r="L18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A19">
         <v>16</v>
       </c>
@@ -3654,26 +4529,35 @@
       <c r="C19" s="4">
         <v>2</v>
       </c>
-      <c r="D19" s="33">
-        <v>0</v>
-      </c>
-      <c r="E19" s="33">
+      <c r="D19">
+        <v>0</v>
+      </c>
+      <c r="E19">
         <v>0</v>
       </c>
       <c r="F19" s="4">
         <v>0</v>
       </c>
-      <c r="G19" s="33">
-        <v>0</v>
-      </c>
-      <c r="H19" s="33">
-        <v>0</v>
-      </c>
-      <c r="I19" s="33">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="G19">
+        <v>0</v>
+      </c>
+      <c r="H19">
+        <v>0</v>
+      </c>
+      <c r="I19" s="4">
+        <v>0</v>
+      </c>
+      <c r="J19">
+        <v>0</v>
+      </c>
+      <c r="K19">
+        <v>0</v>
+      </c>
+      <c r="L19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A20">
         <v>17</v>
       </c>
@@ -3683,26 +4567,35 @@
       <c r="C20" s="4">
         <v>2</v>
       </c>
-      <c r="D20" s="33">
-        <v>0</v>
-      </c>
-      <c r="E20" s="33">
+      <c r="D20">
+        <v>0</v>
+      </c>
+      <c r="E20">
         <v>0</v>
       </c>
       <c r="F20" s="4">
         <v>0</v>
       </c>
-      <c r="G20" s="33">
-        <v>0</v>
-      </c>
-      <c r="H20" s="33">
-        <v>0</v>
-      </c>
-      <c r="I20" s="33">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="G20">
+        <v>0</v>
+      </c>
+      <c r="H20">
+        <v>0</v>
+      </c>
+      <c r="I20" s="4">
+        <v>0</v>
+      </c>
+      <c r="J20">
+        <v>0</v>
+      </c>
+      <c r="K20">
+        <v>0</v>
+      </c>
+      <c r="L20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A21">
         <v>18</v>
       </c>
@@ -3712,26 +4605,35 @@
       <c r="C21" s="4">
         <v>2</v>
       </c>
-      <c r="D21" s="33">
-        <v>0</v>
-      </c>
-      <c r="E21" s="33">
+      <c r="D21">
+        <v>0</v>
+      </c>
+      <c r="E21">
         <v>0</v>
       </c>
       <c r="F21" s="4">
         <v>0</v>
       </c>
-      <c r="G21" s="33">
-        <v>0</v>
-      </c>
-      <c r="H21" s="33">
-        <v>0</v>
-      </c>
-      <c r="I21" s="33">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="G21">
+        <v>0</v>
+      </c>
+      <c r="H21">
+        <v>0</v>
+      </c>
+      <c r="I21" s="4">
+        <v>0</v>
+      </c>
+      <c r="J21">
+        <v>0</v>
+      </c>
+      <c r="K21">
+        <v>0</v>
+      </c>
+      <c r="L21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A22">
         <v>19</v>
       </c>
@@ -3741,26 +4643,35 @@
       <c r="C22" s="4">
         <v>2</v>
       </c>
-      <c r="D22" s="33">
-        <v>0</v>
-      </c>
-      <c r="E22" s="33">
+      <c r="D22">
+        <v>0</v>
+      </c>
+      <c r="E22">
         <v>0</v>
       </c>
       <c r="F22" s="4">
         <v>0</v>
       </c>
-      <c r="G22" s="33">
-        <v>0</v>
-      </c>
-      <c r="H22" s="33">
-        <v>0</v>
-      </c>
-      <c r="I22" s="33">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="G22">
+        <v>0</v>
+      </c>
+      <c r="H22">
+        <v>0</v>
+      </c>
+      <c r="I22" s="4">
+        <v>0</v>
+      </c>
+      <c r="J22">
+        <v>0</v>
+      </c>
+      <c r="K22">
+        <v>0</v>
+      </c>
+      <c r="L22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A23">
         <v>20</v>
       </c>
@@ -3770,26 +4681,35 @@
       <c r="C23" s="4">
         <v>2</v>
       </c>
-      <c r="D23" s="33">
-        <v>0</v>
-      </c>
-      <c r="E23" s="33">
+      <c r="D23">
+        <v>0</v>
+      </c>
+      <c r="E23">
         <v>0</v>
       </c>
       <c r="F23" s="4">
         <v>0</v>
       </c>
-      <c r="G23" s="33">
-        <v>0</v>
-      </c>
-      <c r="H23" s="33">
-        <v>0</v>
-      </c>
-      <c r="I23" s="33">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="G23">
+        <v>0</v>
+      </c>
+      <c r="H23">
+        <v>0</v>
+      </c>
+      <c r="I23" s="4">
+        <v>0</v>
+      </c>
+      <c r="J23">
+        <v>0</v>
+      </c>
+      <c r="K23">
+        <v>0</v>
+      </c>
+      <c r="L23">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A24">
         <v>21</v>
       </c>
@@ -3799,26 +4719,35 @@
       <c r="C24" s="4">
         <v>2</v>
       </c>
-      <c r="D24" s="33">
-        <v>0</v>
-      </c>
-      <c r="E24" s="33">
+      <c r="D24">
+        <v>0</v>
+      </c>
+      <c r="E24">
         <v>0</v>
       </c>
       <c r="F24" s="4">
         <v>0</v>
       </c>
-      <c r="G24" s="33">
-        <v>0</v>
-      </c>
-      <c r="H24" s="33">
-        <v>0</v>
-      </c>
-      <c r="I24" s="33">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="G24">
+        <v>0</v>
+      </c>
+      <c r="H24">
+        <v>0</v>
+      </c>
+      <c r="I24" s="4">
+        <v>0</v>
+      </c>
+      <c r="J24">
+        <v>0</v>
+      </c>
+      <c r="K24">
+        <v>0</v>
+      </c>
+      <c r="L24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A25">
         <v>22</v>
       </c>
@@ -3828,26 +4757,35 @@
       <c r="C25" s="4">
         <v>3</v>
       </c>
-      <c r="D25" s="33">
-        <v>0</v>
-      </c>
-      <c r="E25" s="33">
+      <c r="D25">
+        <v>0</v>
+      </c>
+      <c r="E25">
         <v>0</v>
       </c>
       <c r="F25" s="4">
         <v>0</v>
       </c>
-      <c r="G25" s="33">
-        <v>0</v>
-      </c>
-      <c r="H25" s="33">
-        <v>0</v>
-      </c>
-      <c r="I25" s="33">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="G25">
+        <v>0</v>
+      </c>
+      <c r="H25">
+        <v>0</v>
+      </c>
+      <c r="I25" s="4">
+        <v>0</v>
+      </c>
+      <c r="J25">
+        <v>0</v>
+      </c>
+      <c r="K25">
+        <v>0</v>
+      </c>
+      <c r="L25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A26">
         <v>23</v>
       </c>
@@ -3857,26 +4795,35 @@
       <c r="C26" s="4">
         <v>3</v>
       </c>
-      <c r="D26" s="33">
-        <v>0</v>
-      </c>
-      <c r="E26" s="33">
+      <c r="D26">
+        <v>0</v>
+      </c>
+      <c r="E26">
         <v>0</v>
       </c>
       <c r="F26" s="4">
         <v>0</v>
       </c>
-      <c r="G26" s="33">
-        <v>0</v>
-      </c>
-      <c r="H26" s="33">
-        <v>0</v>
-      </c>
-      <c r="I26" s="33">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="G26">
+        <v>0</v>
+      </c>
+      <c r="H26">
+        <v>0</v>
+      </c>
+      <c r="I26" s="4">
+        <v>0</v>
+      </c>
+      <c r="J26">
+        <v>0</v>
+      </c>
+      <c r="K26">
+        <v>0</v>
+      </c>
+      <c r="L26">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A27">
         <v>24</v>
       </c>
@@ -3886,26 +4833,35 @@
       <c r="C27" s="4">
         <v>3</v>
       </c>
-      <c r="D27" s="33">
-        <v>0</v>
-      </c>
-      <c r="E27" s="33">
+      <c r="D27">
+        <v>0</v>
+      </c>
+      <c r="E27">
         <v>0</v>
       </c>
       <c r="F27" s="4">
         <v>0</v>
       </c>
-      <c r="G27" s="33">
-        <v>0</v>
-      </c>
-      <c r="H27" s="33">
-        <v>0</v>
-      </c>
-      <c r="I27" s="33">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="G27">
+        <v>0</v>
+      </c>
+      <c r="H27">
+        <v>0</v>
+      </c>
+      <c r="I27" s="4">
+        <v>0</v>
+      </c>
+      <c r="J27">
+        <v>0</v>
+      </c>
+      <c r="K27">
+        <v>0</v>
+      </c>
+      <c r="L27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A28">
         <v>25</v>
       </c>
@@ -3915,26 +4871,35 @@
       <c r="C28" s="4">
         <v>3</v>
       </c>
-      <c r="D28" s="33">
-        <v>0</v>
-      </c>
-      <c r="E28" s="33">
+      <c r="D28">
+        <v>0</v>
+      </c>
+      <c r="E28">
         <v>0</v>
       </c>
       <c r="F28" s="4">
         <v>0</v>
       </c>
-      <c r="G28" s="33">
-        <v>0</v>
-      </c>
-      <c r="H28" s="33">
-        <v>0</v>
-      </c>
-      <c r="I28" s="33">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="G28">
+        <v>0</v>
+      </c>
+      <c r="H28">
+        <v>0</v>
+      </c>
+      <c r="I28" s="4">
+        <v>0</v>
+      </c>
+      <c r="J28">
+        <v>0</v>
+      </c>
+      <c r="K28">
+        <v>0</v>
+      </c>
+      <c r="L28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A29">
         <v>26</v>
       </c>
@@ -3944,26 +4909,35 @@
       <c r="C29" s="4">
         <v>3</v>
       </c>
-      <c r="D29" s="33">
-        <v>0</v>
-      </c>
-      <c r="E29" s="33">
+      <c r="D29">
+        <v>0</v>
+      </c>
+      <c r="E29">
         <v>0</v>
       </c>
       <c r="F29" s="4">
         <v>0</v>
       </c>
-      <c r="G29" s="33">
-        <v>0</v>
-      </c>
-      <c r="H29" s="33">
-        <v>0</v>
-      </c>
-      <c r="I29" s="33">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="G29">
+        <v>0</v>
+      </c>
+      <c r="H29">
+        <v>0</v>
+      </c>
+      <c r="I29" s="4">
+        <v>0</v>
+      </c>
+      <c r="J29">
+        <v>0</v>
+      </c>
+      <c r="K29">
+        <v>0</v>
+      </c>
+      <c r="L29">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A30">
         <v>27</v>
       </c>
@@ -3973,26 +4947,35 @@
       <c r="C30" s="4">
         <v>3</v>
       </c>
-      <c r="D30" s="33">
-        <v>0</v>
-      </c>
-      <c r="E30" s="33">
+      <c r="D30">
+        <v>0</v>
+      </c>
+      <c r="E30">
         <v>0</v>
       </c>
       <c r="F30" s="4">
         <v>0</v>
       </c>
-      <c r="G30" s="33">
-        <v>0</v>
-      </c>
-      <c r="H30" s="33">
-        <v>0</v>
-      </c>
-      <c r="I30" s="33">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="31" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="G30">
+        <v>0</v>
+      </c>
+      <c r="H30">
+        <v>0</v>
+      </c>
+      <c r="I30" s="4">
+        <v>0</v>
+      </c>
+      <c r="J30">
+        <v>0</v>
+      </c>
+      <c r="K30">
+        <v>0</v>
+      </c>
+      <c r="L30">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A31">
         <v>28</v>
       </c>
@@ -4002,26 +4985,35 @@
       <c r="C31" s="4">
         <v>3</v>
       </c>
-      <c r="D31" s="33">
-        <v>0</v>
-      </c>
-      <c r="E31" s="33">
+      <c r="D31">
+        <v>0</v>
+      </c>
+      <c r="E31">
         <v>0</v>
       </c>
       <c r="F31" s="4">
         <v>0</v>
       </c>
-      <c r="G31" s="33">
-        <v>0</v>
-      </c>
-      <c r="H31" s="33">
-        <v>0</v>
-      </c>
-      <c r="I31" s="33">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="32" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="G31">
+        <v>0</v>
+      </c>
+      <c r="H31">
+        <v>0</v>
+      </c>
+      <c r="I31" s="4">
+        <v>0</v>
+      </c>
+      <c r="J31">
+        <v>0</v>
+      </c>
+      <c r="K31">
+        <v>0</v>
+      </c>
+      <c r="L31">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A32">
         <v>29</v>
       </c>
@@ -4031,26 +5023,35 @@
       <c r="C32" s="4">
         <v>3</v>
       </c>
-      <c r="D32" s="33">
-        <v>0</v>
-      </c>
-      <c r="E32" s="33">
+      <c r="D32">
+        <v>0</v>
+      </c>
+      <c r="E32">
         <v>0</v>
       </c>
       <c r="F32" s="4">
         <v>0</v>
       </c>
-      <c r="G32" s="33">
-        <v>0</v>
-      </c>
-      <c r="H32" s="33">
-        <v>0</v>
-      </c>
-      <c r="I32" s="33">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="33" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="G32">
+        <v>0</v>
+      </c>
+      <c r="H32">
+        <v>0</v>
+      </c>
+      <c r="I32" s="4">
+        <v>0</v>
+      </c>
+      <c r="J32">
+        <v>0</v>
+      </c>
+      <c r="K32">
+        <v>0</v>
+      </c>
+      <c r="L32">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A33">
         <v>30</v>
       </c>
@@ -4060,26 +5061,35 @@
       <c r="C33" s="4">
         <v>3</v>
       </c>
-      <c r="D33" s="33">
-        <v>0</v>
-      </c>
-      <c r="E33" s="33">
+      <c r="D33">
+        <v>0</v>
+      </c>
+      <c r="E33">
         <v>0</v>
       </c>
       <c r="F33" s="4">
         <v>0</v>
       </c>
-      <c r="G33" s="33">
-        <v>0</v>
-      </c>
-      <c r="H33" s="33">
-        <v>0</v>
-      </c>
-      <c r="I33" s="33">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="34" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="G33">
+        <v>0</v>
+      </c>
+      <c r="H33">
+        <v>0</v>
+      </c>
+      <c r="I33" s="4">
+        <v>0</v>
+      </c>
+      <c r="J33">
+        <v>0</v>
+      </c>
+      <c r="K33">
+        <v>0</v>
+      </c>
+      <c r="L33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A34">
         <v>31</v>
       </c>
@@ -4089,26 +5099,35 @@
       <c r="C34" s="4">
         <v>3</v>
       </c>
-      <c r="D34" s="33">
-        <v>0</v>
-      </c>
-      <c r="E34" s="33">
+      <c r="D34">
+        <v>0</v>
+      </c>
+      <c r="E34">
         <v>0</v>
       </c>
       <c r="F34" s="4">
         <v>0</v>
       </c>
-      <c r="G34" s="33">
-        <v>0</v>
-      </c>
-      <c r="H34" s="33">
-        <v>0</v>
-      </c>
-      <c r="I34" s="33">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="35" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="G34">
+        <v>0</v>
+      </c>
+      <c r="H34">
+        <v>0</v>
+      </c>
+      <c r="I34" s="4">
+        <v>0</v>
+      </c>
+      <c r="J34">
+        <v>0</v>
+      </c>
+      <c r="K34">
+        <v>0</v>
+      </c>
+      <c r="L34">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A35">
         <v>32</v>
       </c>
@@ -4118,22 +5137,31 @@
       <c r="C35" s="4">
         <v>3</v>
       </c>
-      <c r="D35" s="33">
-        <v>0</v>
-      </c>
-      <c r="E35" s="33">
+      <c r="D35">
+        <v>0</v>
+      </c>
+      <c r="E35">
         <v>0</v>
       </c>
       <c r="F35" s="4">
         <v>0</v>
       </c>
-      <c r="G35" s="33">
-        <v>0</v>
-      </c>
-      <c r="H35" s="33">
-        <v>0</v>
-      </c>
-      <c r="I35" s="33">
+      <c r="G35">
+        <v>0</v>
+      </c>
+      <c r="H35">
+        <v>0</v>
+      </c>
+      <c r="I35" s="4">
+        <v>0</v>
+      </c>
+      <c r="J35">
+        <v>0</v>
+      </c>
+      <c r="K35">
+        <v>0</v>
+      </c>
+      <c r="L35">
         <v>0</v>
       </c>
     </row>
